--- a/outputs/operacional/Operacional_Qualidade_Reports.xlsx
+++ b/outputs/operacional/Operacional_Qualidade_Reports.xlsx
@@ -24,8 +24,8 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'4_Apolices_Ativas_c_Cancelamento'!$A$1:$L$14</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'5_Renovacao_Como_Novo'!$A$1:$A$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'6_Situacao_Ativa_Vencida'!$A$1:$L$110</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'7_Acionabilidade_Produtor'!$A$1:$I$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'8_Taxa_Cancelamento'!$A$1:$D$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'7_Acionabilidade_Produtor'!$A$1:$I$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'8_Taxa_Cancelamento'!$A$1:$D$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'9_Run_Context_Guardrails'!$A$1:$K$2</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -495,7 +495,7 @@
     <col width="42" customWidth="1" min="2" max="2"/>
     <col width="19" customWidth="1" min="3" max="3"/>
     <col width="19" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -609,11 +609,11 @@
         <v>100</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>Inútil (constante)</t>
+          <t>Alta</t>
         </is>
       </c>
     </row>
@@ -678,7 +678,7 @@
         <v>100</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>683</v>
+        <v>681</v>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
@@ -701,7 +701,7 @@
         <v>100</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>652</v>
+        <v>638</v>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
@@ -724,11 +724,11 @@
         <v>100</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>Inútil (constante)</t>
+          <t>Alta</t>
         </is>
       </c>
     </row>
@@ -908,7 +908,7 @@
         <v>100</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>779</v>
+        <v>772</v>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
@@ -931,7 +931,7 @@
         <v>100</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>892</v>
+        <v>870</v>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
@@ -1039,13 +1039,13 @@
         <v>2024</v>
       </c>
       <c r="B2" s="4" t="n">
-        <v>690</v>
+        <v>694</v>
       </c>
       <c r="C2" s="4" t="n">
         <v>0</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>690</v>
+        <v>694</v>
       </c>
       <c r="E2" s="4" t="n">
         <v>0</v>
@@ -1056,13 +1056,13 @@
         <v>2025</v>
       </c>
       <c r="B3" s="5" t="n">
-        <v>2058</v>
+        <v>2093</v>
       </c>
       <c r="C3" s="5" t="n">
         <v>0</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>2058</v>
+        <v>2093</v>
       </c>
       <c r="E3" s="5" t="n">
         <v>0</v>
@@ -1073,13 +1073,13 @@
         <v>2026</v>
       </c>
       <c r="B4" s="4" t="n">
-        <v>2023</v>
+        <v>2044</v>
       </c>
       <c r="C4" s="4" t="n">
         <v>0</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>2023</v>
+        <v>2044</v>
       </c>
       <c r="E4" s="4" t="n">
         <v>0</v>
@@ -1090,13 +1090,13 @@
         <v>2027</v>
       </c>
       <c r="B5" s="5" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C5" s="5" t="n">
         <v>0</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E5" s="5" t="n">
         <v>0</v>
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="C2" s="4" t="n">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>53</v>
+        <v>53.7</v>
       </c>
       <c r="E2" s="4" t="b">
         <v>1</v>
@@ -1184,10 +1184,10 @@
         </is>
       </c>
       <c r="C3" s="5" t="n">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>45.7</v>
+        <v>45.5</v>
       </c>
       <c r="E3" s="5" t="b">
         <v>0</v>
@@ -1205,10 +1205,10 @@
         </is>
       </c>
       <c r="C4" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="E4" s="4" t="b">
         <v>0</v>
@@ -1308,7 +1308,7 @@
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>PROD-000421</t>
+          <t>PROD-003618</t>
         </is>
       </c>
       <c r="B2" s="4" t="inlineStr">
@@ -1317,30 +1317,30 @@
         </is>
       </c>
       <c r="C2" s="4" t="n">
-        <v>421</v>
+        <v>3618</v>
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>20644742123</t>
+          <t>01398373540</t>
         </is>
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>TETA</t>
+          <t>BETA</t>
         </is>
       </c>
       <c r="F2" s="4" t="inlineStr">
         <is>
-          <t>EMPRESARIAL</t>
+          <t>EQUIPAMENTOS</t>
         </is>
       </c>
       <c r="G2" s="4" t="inlineStr">
         <is>
-          <t>RC</t>
+          <t>AUTO</t>
         </is>
       </c>
       <c r="H2" s="4" t="n">
-        <v>8028787</v>
+        <v>8281628</v>
       </c>
       <c r="I2" s="4" t="inlineStr">
         <is>
@@ -1358,13 +1358,13 @@
         </is>
       </c>
       <c r="L2" s="6" t="n">
-        <v>45880</v>
+        <v>45647</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>PROD-003422</t>
+          <t>PROD-001916</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
@@ -1373,30 +1373,30 @@
         </is>
       </c>
       <c r="C3" s="5" t="n">
-        <v>3422</v>
+        <v>1916</v>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>26860259222</t>
+          <t>04091570184</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
-          <t>GAMA</t>
+          <t>TETA</t>
         </is>
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>EMPRESARIAL</t>
+          <t>AUTOMÓVEL</t>
         </is>
       </c>
       <c r="G3" s="5" t="inlineStr">
         <is>
-          <t>VIDA</t>
+          <t>AUTO</t>
         </is>
       </c>
       <c r="H3" s="5" t="n">
-        <v>2403738</v>
+        <v>3123388</v>
       </c>
       <c r="I3" s="5" t="inlineStr">
         <is>
@@ -1414,13 +1414,13 @@
         </is>
       </c>
       <c r="L3" s="7" t="n">
-        <v>45891</v>
+        <v>46023</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>PROD-003918</t>
+          <t>PROD-004699</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
@@ -1429,16 +1429,16 @@
         </is>
       </c>
       <c r="C4" s="4" t="n">
-        <v>3918</v>
+        <v>4699</v>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>28685289755</t>
+          <t>07596599920</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>BETA</t>
+          <t>GAMA</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
@@ -1448,11 +1448,11 @@
       </c>
       <c r="G4" s="4" t="inlineStr">
         <is>
-          <t>AUTO</t>
+          <t>RC</t>
         </is>
       </c>
       <c r="H4" s="4" t="n">
-        <v>8281628</v>
+        <v>9286770</v>
       </c>
       <c r="I4" s="4" t="inlineStr">
         <is>
@@ -1470,13 +1470,13 @@
         </is>
       </c>
       <c r="L4" s="6" t="n">
-        <v>45647</v>
+        <v>45540</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>PROD-003219</t>
+          <t>PROD-001754</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
@@ -1485,30 +1485,30 @@
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>3219</v>
+        <v>1754</v>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>40640909743</t>
+          <t>20417929111</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>ZETA</t>
+          <t>ETA</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>RC PROFISSIONAL</t>
+          <t>AUTOMÓVEL</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
-          <t>PATRIMONIAL</t>
+          <t>RC</t>
         </is>
       </c>
       <c r="H5" s="5" t="n">
-        <v>6854013</v>
+        <v>5778306</v>
       </c>
       <c r="I5" s="5" t="inlineStr">
         <is>
@@ -1526,13 +1526,13 @@
         </is>
       </c>
       <c r="L5" s="7" t="n">
-        <v>45751</v>
+        <v>45657</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>PROD-002688</t>
+          <t>PROD-000164</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
@@ -1541,30 +1541,30 @@
         </is>
       </c>
       <c r="C6" s="4" t="n">
-        <v>2688</v>
+        <v>164</v>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>42626551104</t>
+          <t>33173936385</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>TETA</t>
+          <t>ALFA</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>RESIDENCIAL</t>
+          <t>AUTOMÓVEL</t>
         </is>
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>SAÚDE</t>
+          <t>RC</t>
         </is>
       </c>
       <c r="H6" s="4" t="n">
-        <v>3460153</v>
+        <v>9958162</v>
       </c>
       <c r="I6" s="4" t="inlineStr">
         <is>
@@ -1582,13 +1582,13 @@
         </is>
       </c>
       <c r="L6" s="6" t="n">
-        <v>45447</v>
+        <v>46197</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>PROD-002216</t>
+          <t>PROD-002777</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
@@ -1597,30 +1597,30 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>2216</v>
+        <v>2777</v>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>44270312073</t>
+          <t>35031365024</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>TETA</t>
+          <t>GAMA</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>AUTOMÓVEL</t>
+          <t>RC PROFISSIONAL</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>AUTO</t>
+          <t>RC</t>
         </is>
       </c>
       <c r="H7" s="5" t="n">
-        <v>3123388</v>
+        <v>3272041</v>
       </c>
       <c r="I7" s="5" t="inlineStr">
         <is>
@@ -1638,13 +1638,13 @@
         </is>
       </c>
       <c r="L7" s="7" t="n">
-        <v>46023</v>
+        <v>45755</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>PROD-000136</t>
+          <t>PROD-002253</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
@@ -1653,16 +1653,16 @@
         </is>
       </c>
       <c r="C8" s="4" t="n">
-        <v>136</v>
+        <v>2253</v>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>54353462475</t>
+          <t>36403761379</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>GAMA</t>
+          <t>BETA</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
@@ -1676,7 +1676,7 @@
         </is>
       </c>
       <c r="H8" s="4" t="n">
-        <v>8167490</v>
+        <v>7940883</v>
       </c>
       <c r="I8" s="4" t="inlineStr">
         <is>
@@ -1694,13 +1694,13 @@
         </is>
       </c>
       <c r="L8" s="6" t="n">
-        <v>46154</v>
+        <v>45886</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>PROD-002054</t>
+          <t>PROD-002919</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
@@ -1709,30 +1709,30 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>2054</v>
+        <v>2919</v>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>65375564641</t>
+          <t>51820377889</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>ETA</t>
+          <t>ZETA</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>AUTOMÓVEL</t>
+          <t>RC PROFISSIONAL</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
-          <t>RC</t>
+          <t>PATRIMONIAL</t>
         </is>
       </c>
       <c r="H9" s="5" t="n">
-        <v>5778306</v>
+        <v>6854013</v>
       </c>
       <c r="I9" s="5" t="inlineStr">
         <is>
@@ -1750,13 +1750,13 @@
         </is>
       </c>
       <c r="L9" s="7" t="n">
-        <v>45657</v>
+        <v>45751</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>PROD-000715</t>
+          <t>PROD-000415</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
@@ -1765,11 +1765,11 @@
         </is>
       </c>
       <c r="C10" s="4" t="n">
-        <v>715</v>
+        <v>415</v>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>82586736226</t>
+          <t>54788728743</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
@@ -1812,7 +1812,7 @@
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>PROD-003077</t>
+          <t>PROD-000121</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
@@ -1821,21 +1821,21 @@
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>3077</v>
+        <v>121</v>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>83473597746</t>
+          <t>57905528183</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>GAMA</t>
+          <t>TETA</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>RC PROFISSIONAL</t>
+          <t>EMPRESARIAL</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
@@ -1844,7 +1844,7 @@
         </is>
       </c>
       <c r="H11" s="5" t="n">
-        <v>3272041</v>
+        <v>8028787</v>
       </c>
       <c r="I11" s="5" t="inlineStr">
         <is>
@@ -1862,13 +1862,13 @@
         </is>
       </c>
       <c r="L11" s="7" t="n">
-        <v>45755</v>
+        <v>45880</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>PROD-002553</t>
+          <t>PROD-002388</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
@@ -1877,16 +1877,16 @@
         </is>
       </c>
       <c r="C12" s="4" t="n">
-        <v>2553</v>
+        <v>2388</v>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>85474929751</t>
+          <t>62713611155</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>BETA</t>
+          <t>TETA</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
@@ -1896,11 +1896,11 @@
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>PREVIDÊNCIA</t>
+          <t>SAÚDE</t>
         </is>
       </c>
       <c r="H12" s="4" t="n">
-        <v>7940883</v>
+        <v>3460153</v>
       </c>
       <c r="I12" s="4" t="inlineStr">
         <is>
@@ -1918,13 +1918,13 @@
         </is>
       </c>
       <c r="L12" s="6" t="n">
-        <v>45886</v>
+        <v>45447</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>PROD-000464</t>
+          <t>PROD-003122</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
@@ -1933,30 +1933,30 @@
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>464</v>
+        <v>3122</v>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>96520744666</t>
+          <t>93157279194</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>ALFA</t>
+          <t>GAMA</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>AUTOMÓVEL</t>
+          <t>EMPRESARIAL</t>
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
-          <t>RC</t>
+          <t>VIDA</t>
         </is>
       </c>
       <c r="H13" s="5" t="n">
-        <v>9958162</v>
+        <v>2403738</v>
       </c>
       <c r="I13" s="5" t="inlineStr">
         <is>
@@ -1974,13 +1974,13 @@
         </is>
       </c>
       <c r="L13" s="7" t="n">
-        <v>46197</v>
+        <v>45891</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>PROD-002189</t>
+          <t>PROD-001889</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
@@ -1989,11 +1989,11 @@
         </is>
       </c>
       <c r="C14" s="4" t="n">
-        <v>2189</v>
+        <v>1889</v>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>99758172461</t>
+          <t>96499091334</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
@@ -2074,7 +2074,7 @@
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="17" customWidth="1" min="6" max="6"/>
+    <col width="27" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
     <col width="13" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
@@ -2148,7 +2148,7 @@
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>PROD-003188</t>
+          <t>PROD-004472</t>
         </is>
       </c>
       <c r="B2" s="4" t="inlineStr">
@@ -2157,16 +2157,16 @@
         </is>
       </c>
       <c r="C2" s="4" t="n">
-        <v>3188</v>
+        <v>4472</v>
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>03070534578</t>
+          <t>56083318195</t>
         </is>
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>ETA</t>
+          <t>BETA</t>
         </is>
       </c>
       <c r="F2" s="4" t="inlineStr">
@@ -2176,11 +2176,11 @@
       </c>
       <c r="G2" s="4" t="inlineStr">
         <is>
-          <t>VIAGEM</t>
+          <t>VIDA</t>
         </is>
       </c>
       <c r="H2" s="4" t="n">
-        <v>4518266</v>
+        <v>9929073</v>
       </c>
       <c r="I2" s="4" t="inlineStr">
         <is>
@@ -2188,19 +2188,19 @@
         </is>
       </c>
       <c r="J2" s="6" t="n">
-        <v>45472</v>
+        <v>45405</v>
       </c>
       <c r="K2" s="6" t="n">
-        <v>45502</v>
+        <v>45496</v>
       </c>
       <c r="L2" s="4" t="n">
-        <v>694</v>
+        <v>700</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>PROD-004364</t>
+          <t>PROD-002888</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
@@ -2209,16 +2209,16 @@
         </is>
       </c>
       <c r="C3" s="5" t="n">
-        <v>4364</v>
+        <v>2888</v>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>85368663266</t>
+          <t>17535560932</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
-          <t>ZETA</t>
+          <t>ETA</t>
         </is>
       </c>
       <c r="F3" s="5" t="inlineStr">
@@ -2228,11 +2228,11 @@
       </c>
       <c r="G3" s="5" t="inlineStr">
         <is>
-          <t>PATRIMONIAL</t>
+          <t>VIAGEM</t>
         </is>
       </c>
       <c r="H3" s="5" t="n">
-        <v>2870254</v>
+        <v>4518266</v>
       </c>
       <c r="I3" s="5" t="inlineStr">
         <is>
@@ -2240,19 +2240,19 @@
         </is>
       </c>
       <c r="J3" s="7" t="n">
-        <v>45520</v>
+        <v>45472</v>
       </c>
       <c r="K3" s="7" t="n">
-        <v>45612</v>
+        <v>45502</v>
       </c>
       <c r="L3" s="5" t="n">
-        <v>584</v>
+        <v>694</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>PROD-002147</t>
+          <t>PROD-001548</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
@@ -2261,30 +2261,30 @@
         </is>
       </c>
       <c r="C4" s="4" t="n">
-        <v>2147</v>
+        <v>1548</v>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>42843479552</t>
+          <t>23884969653</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>TETA</t>
+          <t>DELT</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>VIAGEM</t>
+          <t>EQUIPAMENTOS</t>
         </is>
       </c>
       <c r="G4" s="4" t="inlineStr">
         <is>
-          <t>PATRIMONIAL</t>
+          <t>SAÚDE</t>
         </is>
       </c>
       <c r="H4" s="4" t="n">
-        <v>7320381</v>
+        <v>4792077</v>
       </c>
       <c r="I4" s="4" t="inlineStr">
         <is>
@@ -2292,19 +2292,19 @@
         </is>
       </c>
       <c r="J4" s="6" t="n">
-        <v>45626</v>
+        <v>45538</v>
       </c>
       <c r="K4" s="6" t="n">
-        <v>45656</v>
+        <v>45508</v>
       </c>
       <c r="L4" s="4" t="n">
-        <v>540</v>
+        <v>688</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>PROD-003488</t>
+          <t>PROD-004064</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
@@ -2313,16 +2313,16 @@
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>3488</v>
+        <v>4064</v>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>08740640391</t>
+          <t>57437489691</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>ETA</t>
+          <t>ZETA</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
@@ -2332,11 +2332,11 @@
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
-          <t>VIDA</t>
+          <t>PATRIMONIAL</t>
         </is>
       </c>
       <c r="H5" s="5" t="n">
-        <v>7932687</v>
+        <v>2870254</v>
       </c>
       <c r="I5" s="5" t="inlineStr">
         <is>
@@ -2344,19 +2344,19 @@
         </is>
       </c>
       <c r="J5" s="7" t="n">
-        <v>45631</v>
+        <v>45520</v>
       </c>
       <c r="K5" s="7" t="n">
-        <v>45662</v>
+        <v>45612</v>
       </c>
       <c r="L5" s="5" t="n">
-        <v>534</v>
+        <v>584</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>PROD-002584</t>
+          <t>PROD-001847</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
@@ -2365,16 +2365,16 @@
         </is>
       </c>
       <c r="C6" s="4" t="n">
-        <v>2584</v>
+        <v>1847</v>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>55231491357</t>
+          <t>02278469973</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>ETA</t>
+          <t>TETA</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
@@ -2384,11 +2384,11 @@
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>SAÚDE</t>
+          <t>PATRIMONIAL</t>
         </is>
       </c>
       <c r="H6" s="4" t="n">
-        <v>6232620</v>
+        <v>7320381</v>
       </c>
       <c r="I6" s="4" t="inlineStr">
         <is>
@@ -2396,19 +2396,19 @@
         </is>
       </c>
       <c r="J6" s="6" t="n">
-        <v>45680</v>
+        <v>45626</v>
       </c>
       <c r="K6" s="6" t="n">
-        <v>45739</v>
+        <v>45656</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>457</v>
+        <v>540</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>PROD-000792</t>
+          <t>PROD-003188</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
@@ -2417,16 +2417,16 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>792</v>
+        <v>3188</v>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>95701543039</t>
+          <t>46591166553</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>ZETA</t>
+          <t>ETA</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
@@ -2436,11 +2436,11 @@
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>AUTO</t>
+          <t>VIDA</t>
         </is>
       </c>
       <c r="H7" s="5" t="n">
-        <v>8944908</v>
+        <v>7932687</v>
       </c>
       <c r="I7" s="5" t="inlineStr">
         <is>
@@ -2448,19 +2448,19 @@
         </is>
       </c>
       <c r="J7" s="7" t="n">
-        <v>45665</v>
+        <v>45631</v>
       </c>
       <c r="K7" s="7" t="n">
-        <v>45755</v>
+        <v>45662</v>
       </c>
       <c r="L7" s="5" t="n">
-        <v>441</v>
+        <v>534</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>PROD-000698</t>
+          <t>PROD-002284</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
@@ -2469,30 +2469,30 @@
         </is>
       </c>
       <c r="C8" s="4" t="n">
-        <v>698</v>
+        <v>2284</v>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>82586736226</t>
+          <t>71236851604</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>TETA</t>
+          <t>ETA</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>RC PROFISSIONAL</t>
+          <t>VIAGEM</t>
         </is>
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>VIDA</t>
+          <t>SAÚDE</t>
         </is>
       </c>
       <c r="H8" s="4" t="n">
-        <v>7602571</v>
+        <v>6232620</v>
       </c>
       <c r="I8" s="4" t="inlineStr">
         <is>
@@ -2500,19 +2500,19 @@
         </is>
       </c>
       <c r="J8" s="6" t="n">
-        <v>45392</v>
+        <v>45680</v>
       </c>
       <c r="K8" s="6" t="n">
-        <v>45757</v>
+        <v>45739</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>439</v>
+        <v>457</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>PROD-002125</t>
+          <t>PROD-000492</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
@@ -2521,30 +2521,30 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>2125</v>
+        <v>492</v>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>13433200379</t>
+          <t>37562890028</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>TETA</t>
+          <t>ZETA</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>AUTOMÓVEL</t>
+          <t>VIAGEM</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
-          <t>PREVIDÊNCIA</t>
+          <t>AUTO</t>
         </is>
       </c>
       <c r="H9" s="5" t="n">
-        <v>3067132</v>
+        <v>8944908</v>
       </c>
       <c r="I9" s="5" t="inlineStr">
         <is>
@@ -2552,19 +2552,19 @@
         </is>
       </c>
       <c r="J9" s="7" t="n">
-        <v>45400</v>
+        <v>45665</v>
       </c>
       <c r="K9" s="7" t="n">
-        <v>45765</v>
+        <v>45755</v>
       </c>
       <c r="L9" s="5" t="n">
-        <v>431</v>
+        <v>441</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>PROD-000256</t>
+          <t>PROD-000398</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
@@ -2573,16 +2573,16 @@
         </is>
       </c>
       <c r="C10" s="4" t="n">
-        <v>256</v>
+        <v>398</v>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>53926442209</t>
+          <t>54788728743</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>ALFA</t>
+          <t>TETA</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
@@ -2592,11 +2592,11 @@
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>PREVIDÊNCIA</t>
+          <t>VIDA</t>
         </is>
       </c>
       <c r="H10" s="4" t="n">
-        <v>1545449</v>
+        <v>7602571</v>
       </c>
       <c r="I10" s="4" t="inlineStr">
         <is>
@@ -2604,19 +2604,19 @@
         </is>
       </c>
       <c r="J10" s="6" t="n">
-        <v>45402</v>
+        <v>45392</v>
       </c>
       <c r="K10" s="6" t="n">
-        <v>45767</v>
+        <v>45757</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>429</v>
+        <v>439</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>PROD-002758</t>
+          <t>PROD-004682</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
@@ -2625,30 +2625,30 @@
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>2758</v>
+        <v>4682</v>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>02786814473</t>
+          <t>59831244129</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>BETA</t>
+          <t>ALFA</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>EQUIPAMENTOS</t>
+          <t>RC PROFISSIONAL</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>AUTO</t>
+          <t>RC</t>
         </is>
       </c>
       <c r="H11" s="5" t="n">
-        <v>3489483</v>
+        <v>9707237</v>
       </c>
       <c r="I11" s="5" t="inlineStr">
         <is>
@@ -2656,19 +2656,19 @@
         </is>
       </c>
       <c r="J11" s="7" t="n">
-        <v>45412</v>
+        <v>45399</v>
       </c>
       <c r="K11" s="7" t="n">
-        <v>45777</v>
+        <v>45764</v>
       </c>
       <c r="L11" s="5" t="n">
-        <v>419</v>
+        <v>432</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>PROD-001672</t>
+          <t>PROD-001825</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
@@ -2677,11 +2677,11 @@
         </is>
       </c>
       <c r="C12" s="4" t="n">
-        <v>1672</v>
+        <v>1825</v>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>41395376724</t>
+          <t>59255562588</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
@@ -2691,16 +2691,16 @@
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>EMPRESARIAL</t>
+          <t>AUTOMÓVEL</t>
         </is>
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>VIDA</t>
+          <t>PREVIDÊNCIA</t>
         </is>
       </c>
       <c r="H12" s="4" t="n">
-        <v>7037761</v>
+        <v>3067132</v>
       </c>
       <c r="I12" s="4" t="inlineStr">
         <is>
@@ -2708,19 +2708,19 @@
         </is>
       </c>
       <c r="J12" s="6" t="n">
-        <v>45422</v>
+        <v>45400</v>
       </c>
       <c r="K12" s="6" t="n">
-        <v>45787</v>
+        <v>45765</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>409</v>
+        <v>431</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>PROD-002687</t>
+          <t>PROD-002458</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
@@ -2729,30 +2729,30 @@
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>2687</v>
+        <v>2458</v>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>42626551104</t>
+          <t>17187026217</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>TETA</t>
+          <t>BETA</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>RESIDENCIAL</t>
+          <t>EQUIPAMENTOS</t>
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
-          <t>SAÚDE</t>
+          <t>AUTO</t>
         </is>
       </c>
       <c r="H13" s="5" t="n">
-        <v>3460153</v>
+        <v>3489483</v>
       </c>
       <c r="I13" s="5" t="inlineStr">
         <is>
@@ -2760,19 +2760,19 @@
         </is>
       </c>
       <c r="J13" s="7" t="n">
-        <v>45427</v>
+        <v>45412</v>
       </c>
       <c r="K13" s="7" t="n">
-        <v>45792</v>
+        <v>45777</v>
       </c>
       <c r="L13" s="5" t="n">
-        <v>404</v>
+        <v>419</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>PROD-003442</t>
+          <t>PROD-001372</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
@@ -2781,30 +2781,30 @@
         </is>
       </c>
       <c r="C14" s="4" t="n">
-        <v>3442</v>
+        <v>1372</v>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>27111161528</t>
+          <t>61847870050</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>ETA</t>
+          <t>TETA</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>VIAGEM</t>
+          <t>EMPRESARIAL</t>
         </is>
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>PREVIDÊNCIA</t>
+          <t>VIDA</t>
         </is>
       </c>
       <c r="H14" s="4" t="n">
-        <v>4275627</v>
+        <v>7037761</v>
       </c>
       <c r="I14" s="4" t="inlineStr">
         <is>
@@ -2812,19 +2812,19 @@
         </is>
       </c>
       <c r="J14" s="6" t="n">
-        <v>45706</v>
+        <v>45422</v>
       </c>
       <c r="K14" s="6" t="n">
-        <v>45795</v>
+        <v>45787</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>401</v>
+        <v>409</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>PROD-002423</t>
+          <t>PROD-002387</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
@@ -2833,30 +2833,30 @@
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>2423</v>
+        <v>2387</v>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>54868740345</t>
+          <t>62713611155</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>ZETA</t>
+          <t>TETA</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>EQUIPAMENTOS</t>
+          <t>RESIDENCIAL</t>
         </is>
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>VIAGEM</t>
+          <t>SAÚDE</t>
         </is>
       </c>
       <c r="H15" s="5" t="n">
-        <v>6074298</v>
+        <v>3460153</v>
       </c>
       <c r="I15" s="5" t="inlineStr">
         <is>
@@ -2864,19 +2864,19 @@
         </is>
       </c>
       <c r="J15" s="7" t="n">
-        <v>45436</v>
+        <v>45427</v>
       </c>
       <c r="K15" s="7" t="n">
-        <v>45801</v>
+        <v>45792</v>
       </c>
       <c r="L15" s="5" t="n">
-        <v>395</v>
+        <v>404</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>PROD-002499</t>
+          <t>PROD-003142</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
@@ -2885,16 +2885,16 @@
         </is>
       </c>
       <c r="C16" s="4" t="n">
-        <v>2499</v>
+        <v>3142</v>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>86753396360</t>
+          <t>04556110022</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>ÉPSI</t>
+          <t>ETA</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
@@ -2904,11 +2904,11 @@
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>VIDA</t>
+          <t>PREVIDÊNCIA</t>
         </is>
       </c>
       <c r="H16" s="4" t="n">
-        <v>4576858</v>
+        <v>4275627</v>
       </c>
       <c r="I16" s="4" t="inlineStr">
         <is>
@@ -2916,19 +2916,19 @@
         </is>
       </c>
       <c r="J16" s="6" t="n">
-        <v>45752</v>
+        <v>45706</v>
       </c>
       <c r="K16" s="6" t="n">
-        <v>45813</v>
+        <v>45795</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>383</v>
+        <v>401</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>PROD-001186</t>
+          <t>PROD-002123</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
@@ -2937,30 +2937,30 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>1186</v>
+        <v>2123</v>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>64240082547</t>
+          <t>89994043898</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>DELT</t>
+          <t>ZETA</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>RESIDENCIAL</t>
+          <t>EQUIPAMENTOS</t>
         </is>
       </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t>PATRIMONIAL</t>
+          <t>VIAGEM</t>
         </is>
       </c>
       <c r="H17" s="5" t="n">
-        <v>3355474</v>
+        <v>6074298</v>
       </c>
       <c r="I17" s="5" t="inlineStr">
         <is>
@@ -2968,19 +2968,19 @@
         </is>
       </c>
       <c r="J17" s="7" t="n">
-        <v>45448</v>
+        <v>45436</v>
       </c>
       <c r="K17" s="7" t="n">
-        <v>45813</v>
+        <v>45801</v>
       </c>
       <c r="L17" s="5" t="n">
-        <v>383</v>
+        <v>395</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>PROD-000153</t>
+          <t>PROD-000886</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
@@ -2989,30 +2989,30 @@
         </is>
       </c>
       <c r="C18" s="4" t="n">
-        <v>153</v>
+        <v>886</v>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>36403761379</t>
+          <t>83473597746</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>ZETA</t>
+          <t>DELT</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>EMPRESARIAL</t>
+          <t>RESIDENCIAL</t>
         </is>
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>SAÚDE</t>
+          <t>PATRIMONIAL</t>
         </is>
       </c>
       <c r="H18" s="4" t="n">
-        <v>1288432</v>
+        <v>3355474</v>
       </c>
       <c r="I18" s="4" t="inlineStr">
         <is>
@@ -3020,19 +3020,19 @@
         </is>
       </c>
       <c r="J18" s="6" t="n">
-        <v>45452</v>
+        <v>45448</v>
       </c>
       <c r="K18" s="6" t="n">
-        <v>45817</v>
+        <v>45813</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>379</v>
+        <v>383</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>PROD-001834</t>
+          <t>PROD-002199</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
@@ -3041,11 +3041,11 @@
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>1834</v>
+        <v>2199</v>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>89994043898</t>
+          <t>39382761539</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -3055,16 +3055,16 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>RESIDENCIAL</t>
+          <t>VIAGEM</t>
         </is>
       </c>
       <c r="G19" s="5" t="inlineStr">
         <is>
-          <t>AUTO</t>
+          <t>VIDA</t>
         </is>
       </c>
       <c r="H19" s="5" t="n">
-        <v>1818971</v>
+        <v>4576858</v>
       </c>
       <c r="I19" s="5" t="inlineStr">
         <is>
@@ -3072,19 +3072,19 @@
         </is>
       </c>
       <c r="J19" s="7" t="n">
-        <v>45454</v>
+        <v>45752</v>
       </c>
       <c r="K19" s="7" t="n">
-        <v>45819</v>
+        <v>45813</v>
       </c>
       <c r="L19" s="5" t="n">
-        <v>377</v>
+        <v>383</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>PROD-002374</t>
+          <t>PROD-001534</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
@@ -3093,11 +3093,11 @@
         </is>
       </c>
       <c r="C20" s="4" t="n">
-        <v>2374</v>
+        <v>1534</v>
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>07432927129</t>
+          <t>96561014388</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
@@ -3107,16 +3107,16 @@
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>EMPRESARIAL</t>
+          <t>RESIDENCIAL</t>
         </is>
       </c>
       <c r="G20" s="4" t="inlineStr">
         <is>
-          <t>VIAGEM</t>
+          <t>AUTO</t>
         </is>
       </c>
       <c r="H20" s="4" t="n">
-        <v>9660068</v>
+        <v>1818971</v>
       </c>
       <c r="I20" s="4" t="inlineStr">
         <is>
@@ -3124,19 +3124,19 @@
         </is>
       </c>
       <c r="J20" s="6" t="n">
-        <v>45456</v>
+        <v>45454</v>
       </c>
       <c r="K20" s="6" t="n">
-        <v>45821</v>
+        <v>45819</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>PROD-003691</t>
+          <t>PROD-002074</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
@@ -3145,30 +3145,30 @@
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>3691</v>
+        <v>2074</v>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>81273585730</t>
+          <t>14429444019</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>TETA</t>
+          <t>ÉPSI</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>EQUIPAMENTOS</t>
+          <t>EMPRESARIAL</t>
         </is>
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>SAÚDE</t>
+          <t>VIAGEM</t>
         </is>
       </c>
       <c r="H21" s="5" t="n">
-        <v>4891930</v>
+        <v>9660068</v>
       </c>
       <c r="I21" s="5" t="inlineStr">
         <is>
@@ -3176,19 +3176,19 @@
         </is>
       </c>
       <c r="J21" s="7" t="n">
-        <v>45464</v>
+        <v>45456</v>
       </c>
       <c r="K21" s="7" t="n">
-        <v>45829</v>
+        <v>45821</v>
       </c>
       <c r="L21" s="5" t="n">
-        <v>367</v>
+        <v>375</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>PROD-002134</t>
+          <t>PROD-003391</t>
         </is>
       </c>
       <c r="B22" s="4" t="inlineStr">
@@ -3197,30 +3197,30 @@
         </is>
       </c>
       <c r="C22" s="4" t="n">
-        <v>2134</v>
+        <v>3391</v>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>68011280598</t>
+          <t>55449647598</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>ZETA</t>
+          <t>TETA</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>AUTOMÓVEL</t>
+          <t>EQUIPAMENTOS</t>
         </is>
       </c>
       <c r="G22" s="4" t="inlineStr">
         <is>
-          <t>RC</t>
+          <t>SAÚDE</t>
         </is>
       </c>
       <c r="H22" s="4" t="n">
-        <v>3742610</v>
+        <v>4891930</v>
       </c>
       <c r="I22" s="4" t="inlineStr">
         <is>
@@ -3228,19 +3228,19 @@
         </is>
       </c>
       <c r="J22" s="6" t="n">
-        <v>45469</v>
+        <v>45464</v>
       </c>
       <c r="K22" s="6" t="n">
-        <v>45834</v>
+        <v>45829</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>362</v>
+        <v>367</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>PROD-002452</t>
+          <t>PROD-001834</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
@@ -3249,21 +3249,21 @@
         </is>
       </c>
       <c r="C23" s="5" t="n">
-        <v>2452</v>
+        <v>1834</v>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>77418625652</t>
+          <t>22535841438</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>DELT</t>
+          <t>ZETA</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>VIAGEM</t>
+          <t>AUTOMÓVEL</t>
         </is>
       </c>
       <c r="G23" s="5" t="inlineStr">
@@ -3272,7 +3272,7 @@
         </is>
       </c>
       <c r="H23" s="5" t="n">
-        <v>7091258</v>
+        <v>3742610</v>
       </c>
       <c r="I23" s="5" t="inlineStr">
         <is>
@@ -3280,19 +3280,19 @@
         </is>
       </c>
       <c r="J23" s="7" t="n">
-        <v>45743</v>
+        <v>45469</v>
       </c>
       <c r="K23" s="7" t="n">
-        <v>45835</v>
+        <v>45834</v>
       </c>
       <c r="L23" s="5" t="n">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>PROD-004778</t>
+          <t>PROD-002152</t>
         </is>
       </c>
       <c r="B24" s="4" t="inlineStr">
@@ -3301,11 +3301,11 @@
         </is>
       </c>
       <c r="C24" s="4" t="n">
-        <v>4778</v>
+        <v>2152</v>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>77418625652</t>
+          <t>12499856984</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
@@ -3344,7 +3344,7 @@
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>PROD-003285</t>
+          <t>PROD-002985</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
@@ -3353,11 +3353,11 @@
         </is>
       </c>
       <c r="C25" s="5" t="n">
-        <v>3285</v>
+        <v>2985</v>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>39103717058</t>
+          <t>02843959953</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -3396,7 +3396,7 @@
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>PROD-003660</t>
+          <t>PROD-004758</t>
         </is>
       </c>
       <c r="B26" s="4" t="inlineStr">
@@ -3405,16 +3405,16 @@
         </is>
       </c>
       <c r="C26" s="4" t="n">
-        <v>3660</v>
+        <v>4758</v>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>25462914865</t>
+          <t>40321153550</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>ETA</t>
+          <t>BETA</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
@@ -3424,11 +3424,11 @@
       </c>
       <c r="G26" s="4" t="inlineStr">
         <is>
-          <t>SAÚDE</t>
+          <t>PATRIMONIAL</t>
         </is>
       </c>
       <c r="H26" s="4" t="n">
-        <v>1569792</v>
+        <v>4544803</v>
       </c>
       <c r="I26" s="4" t="inlineStr">
         <is>
@@ -3436,19 +3436,19 @@
         </is>
       </c>
       <c r="J26" s="6" t="n">
-        <v>45491</v>
+        <v>45477</v>
       </c>
       <c r="K26" s="6" t="n">
-        <v>45856</v>
+        <v>45842</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>340</v>
+        <v>354</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>PROD-002785</t>
+          <t>PROD-003360</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
@@ -3457,30 +3457,30 @@
         </is>
       </c>
       <c r="C27" s="5" t="n">
-        <v>2785</v>
+        <v>3360</v>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>63942788165</t>
+          <t>79968460810</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>ALFA</t>
+          <t>ETA</t>
         </is>
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>EQUIPAMENTOS</t>
+          <t>RC PROFISSIONAL</t>
         </is>
       </c>
       <c r="G27" s="5" t="inlineStr">
         <is>
-          <t>VIDA</t>
+          <t>SAÚDE</t>
         </is>
       </c>
       <c r="H27" s="5" t="n">
-        <v>4982314</v>
+        <v>1569792</v>
       </c>
       <c r="I27" s="5" t="inlineStr">
         <is>
@@ -3488,19 +3488,19 @@
         </is>
       </c>
       <c r="J27" s="7" t="n">
-        <v>45497</v>
+        <v>45491</v>
       </c>
       <c r="K27" s="7" t="n">
-        <v>45862</v>
+        <v>45856</v>
       </c>
       <c r="L27" s="5" t="n">
-        <v>334</v>
+        <v>340</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>PROD-001287</t>
+          <t>PROD-002485</t>
         </is>
       </c>
       <c r="B28" s="4" t="inlineStr">
@@ -3509,30 +3509,30 @@
         </is>
       </c>
       <c r="C28" s="4" t="n">
-        <v>1287</v>
+        <v>2485</v>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>80392827229</t>
+          <t>31752071678</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>DELT</t>
+          <t>ALFA</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>VIAGEM</t>
+          <t>EQUIPAMENTOS</t>
         </is>
       </c>
       <c r="G28" s="4" t="inlineStr">
         <is>
-          <t>PREVIDÊNCIA</t>
+          <t>VIDA</t>
         </is>
       </c>
       <c r="H28" s="4" t="n">
-        <v>1898452</v>
+        <v>4982314</v>
       </c>
       <c r="I28" s="4" t="inlineStr">
         <is>
@@ -3540,19 +3540,19 @@
         </is>
       </c>
       <c r="J28" s="6" t="n">
-        <v>45893</v>
+        <v>45497</v>
       </c>
       <c r="K28" s="6" t="n">
-        <v>45863</v>
+        <v>45862</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>PROD-004407</t>
+          <t>PROD-004107</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
@@ -3561,11 +3561,11 @@
         </is>
       </c>
       <c r="C29" s="5" t="n">
-        <v>4407</v>
+        <v>4107</v>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>91846386557</t>
+          <t>04341651827</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -3604,7 +3604,7 @@
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>PROD-004396</t>
+          <t>PROD-004592</t>
         </is>
       </c>
       <c r="B30" s="4" t="inlineStr">
@@ -3613,16 +3613,16 @@
         </is>
       </c>
       <c r="C30" s="4" t="n">
-        <v>4396</v>
+        <v>4592</v>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>57924991251</t>
+          <t>85524140602</t>
         </is>
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>GAMA</t>
+          <t>TETA</t>
         </is>
       </c>
       <c r="F30" s="4" t="inlineStr">
@@ -3632,11 +3632,11 @@
       </c>
       <c r="G30" s="4" t="inlineStr">
         <is>
-          <t>RC</t>
+          <t>VIDA</t>
         </is>
       </c>
       <c r="H30" s="4" t="n">
-        <v>4795425</v>
+        <v>6585969</v>
       </c>
       <c r="I30" s="4" t="inlineStr">
         <is>
@@ -3644,19 +3644,19 @@
         </is>
       </c>
       <c r="J30" s="6" t="n">
-        <v>45788</v>
+        <v>45781</v>
       </c>
       <c r="K30" s="6" t="n">
-        <v>45880</v>
+        <v>45873</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>316</v>
+        <v>323</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>PROD-002946</t>
+          <t>PROD-004096</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
@@ -3665,16 +3665,16 @@
         </is>
       </c>
       <c r="C31" s="5" t="n">
-        <v>2946</v>
+        <v>4096</v>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>78774701687</t>
+          <t>51256746807</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
-          <t>DELT</t>
+          <t>GAMA</t>
         </is>
       </c>
       <c r="F31" s="5" t="inlineStr">
@@ -3684,11 +3684,11 @@
       </c>
       <c r="G31" s="5" t="inlineStr">
         <is>
-          <t>SAÚDE</t>
+          <t>RC</t>
         </is>
       </c>
       <c r="H31" s="5" t="n">
-        <v>6384807</v>
+        <v>4795425</v>
       </c>
       <c r="I31" s="5" t="inlineStr">
         <is>
@@ -3696,19 +3696,19 @@
         </is>
       </c>
       <c r="J31" s="7" t="n">
-        <v>45850</v>
+        <v>45788</v>
       </c>
       <c r="K31" s="7" t="n">
-        <v>45881</v>
+        <v>45880</v>
       </c>
       <c r="L31" s="5" t="n">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>PROD-002314</t>
+          <t>PROD-002646</t>
         </is>
       </c>
       <c r="B32" s="4" t="inlineStr">
@@ -3717,30 +3717,30 @@
         </is>
       </c>
       <c r="C32" s="4" t="n">
-        <v>2314</v>
+        <v>2646</v>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>38663177971</t>
+          <t>22499982795</t>
         </is>
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>ETA</t>
+          <t>DELT</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>RESIDENCIAL</t>
+          <t>VIAGEM</t>
         </is>
       </c>
       <c r="G32" s="4" t="inlineStr">
         <is>
-          <t>PREVIDÊNCIA</t>
+          <t>SAÚDE</t>
         </is>
       </c>
       <c r="H32" s="4" t="n">
-        <v>3438906</v>
+        <v>6384807</v>
       </c>
       <c r="I32" s="4" t="inlineStr">
         <is>
@@ -3748,19 +3748,19 @@
         </is>
       </c>
       <c r="J32" s="6" t="n">
-        <v>45517</v>
+        <v>45850</v>
       </c>
       <c r="K32" s="6" t="n">
-        <v>45882</v>
+        <v>45881</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>PROD-001195</t>
+          <t>PROD-002014</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
@@ -3769,30 +3769,30 @@
         </is>
       </c>
       <c r="C33" s="5" t="n">
-        <v>1195</v>
+        <v>2014</v>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>45547813767</t>
+          <t>71422410988</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
-          <t>DELT</t>
+          <t>ETA</t>
         </is>
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>EMPRESARIAL</t>
+          <t>RESIDENCIAL</t>
         </is>
       </c>
       <c r="G33" s="5" t="inlineStr">
         <is>
-          <t>SAÚDE</t>
+          <t>PREVIDÊNCIA</t>
         </is>
       </c>
       <c r="H33" s="5" t="n">
-        <v>9908966</v>
+        <v>3438906</v>
       </c>
       <c r="I33" s="5" t="inlineStr">
         <is>
@@ -3800,19 +3800,19 @@
         </is>
       </c>
       <c r="J33" s="7" t="n">
-        <v>45518</v>
+        <v>45517</v>
       </c>
       <c r="K33" s="7" t="n">
-        <v>45883</v>
+        <v>45882</v>
       </c>
       <c r="L33" s="5" t="n">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>PROD-000892</t>
+          <t>PROD-000895</t>
         </is>
       </c>
       <c r="B34" s="4" t="inlineStr">
@@ -3821,30 +3821,30 @@
         </is>
       </c>
       <c r="C34" s="4" t="n">
-        <v>892</v>
+        <v>895</v>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>19148564679</t>
+          <t>15313636317</t>
         </is>
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>ZETA</t>
+          <t>DELT</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>RESIDENCIAL</t>
+          <t>EMPRESARIAL</t>
         </is>
       </c>
       <c r="G34" s="4" t="inlineStr">
         <is>
-          <t>VIAGEM</t>
+          <t>SAÚDE</t>
         </is>
       </c>
       <c r="H34" s="4" t="n">
-        <v>3763744</v>
+        <v>9908966</v>
       </c>
       <c r="I34" s="4" t="inlineStr">
         <is>
@@ -3864,7 +3864,7 @@
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>PROD-004405</t>
+          <t>PROD-000592</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
@@ -3873,21 +3873,21 @@
         </is>
       </c>
       <c r="C35" s="5" t="n">
-        <v>4405</v>
+        <v>592</v>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>91846386557</t>
+          <t>56475705120</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
-          <t>DELT</t>
+          <t>ZETA</t>
         </is>
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>EMPRESARIAL</t>
+          <t>RESIDENCIAL</t>
         </is>
       </c>
       <c r="G35" s="5" t="inlineStr">
@@ -3896,7 +3896,7 @@
         </is>
       </c>
       <c r="H35" s="5" t="n">
-        <v>9121780</v>
+        <v>3763744</v>
       </c>
       <c r="I35" s="5" t="inlineStr">
         <is>
@@ -3904,19 +3904,19 @@
         </is>
       </c>
       <c r="J35" s="7" t="n">
-        <v>45521</v>
+        <v>45518</v>
       </c>
       <c r="K35" s="7" t="n">
-        <v>45886</v>
+        <v>45883</v>
       </c>
       <c r="L35" s="5" t="n">
-        <v>310</v>
+        <v>313</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>PROD-002313</t>
+          <t>PROD-004698</t>
         </is>
       </c>
       <c r="B36" s="4" t="inlineStr">
@@ -3925,30 +3925,30 @@
         </is>
       </c>
       <c r="C36" s="4" t="n">
-        <v>2313</v>
+        <v>4698</v>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>27128639174</t>
+          <t>07596599920</t>
         </is>
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>BETA</t>
+          <t>GAMA</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>RESIDENCIAL</t>
+          <t>EQUIPAMENTOS</t>
         </is>
       </c>
       <c r="G36" s="4" t="inlineStr">
         <is>
-          <t>PREVIDÊNCIA</t>
+          <t>RC</t>
         </is>
       </c>
       <c r="H36" s="4" t="n">
-        <v>4603263</v>
+        <v>9286770</v>
       </c>
       <c r="I36" s="4" t="inlineStr">
         <is>
@@ -3956,19 +3956,19 @@
         </is>
       </c>
       <c r="J36" s="6" t="n">
-        <v>45524</v>
+        <v>45520</v>
       </c>
       <c r="K36" s="6" t="n">
-        <v>45889</v>
+        <v>45885</v>
       </c>
       <c r="L36" s="4" t="n">
-        <v>307</v>
+        <v>311</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>PROD-001353</t>
+          <t>PROD-004105</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
@@ -3977,30 +3977,30 @@
         </is>
       </c>
       <c r="C37" s="5" t="n">
-        <v>1353</v>
+        <v>4105</v>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>48640155778</t>
+          <t>04341651827</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
         <is>
-          <t>ÉPSI</t>
+          <t>DELT</t>
         </is>
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>RESIDENCIAL</t>
+          <t>EMPRESARIAL</t>
         </is>
       </c>
       <c r="G37" s="5" t="inlineStr">
         <is>
-          <t>SAÚDE</t>
+          <t>VIAGEM</t>
         </is>
       </c>
       <c r="H37" s="5" t="n">
-        <v>7743856</v>
+        <v>9121780</v>
       </c>
       <c r="I37" s="5" t="inlineStr">
         <is>
@@ -4008,19 +4008,19 @@
         </is>
       </c>
       <c r="J37" s="7" t="n">
-        <v>45525</v>
+        <v>45521</v>
       </c>
       <c r="K37" s="7" t="n">
-        <v>45890</v>
+        <v>45886</v>
       </c>
       <c r="L37" s="5" t="n">
-        <v>306</v>
+        <v>310</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>PROD-000673</t>
+          <t>PROD-002013</t>
         </is>
       </c>
       <c r="B38" s="4" t="inlineStr">
@@ -4029,11 +4029,11 @@
         </is>
       </c>
       <c r="C38" s="4" t="n">
-        <v>673</v>
+        <v>2013</v>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>05129276637</t>
+          <t>27570596401</t>
         </is>
       </c>
       <c r="E38" s="4" t="inlineStr">
@@ -4043,16 +4043,16 @@
       </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
-          <t>VIAGEM</t>
+          <t>RESIDENCIAL</t>
         </is>
       </c>
       <c r="G38" s="4" t="inlineStr">
         <is>
-          <t>SAÚDE</t>
+          <t>PREVIDÊNCIA</t>
         </is>
       </c>
       <c r="H38" s="4" t="n">
-        <v>6075106</v>
+        <v>4603263</v>
       </c>
       <c r="I38" s="4" t="inlineStr">
         <is>
@@ -4060,19 +4060,19 @@
         </is>
       </c>
       <c r="J38" s="6" t="n">
-        <v>45837</v>
+        <v>45524</v>
       </c>
       <c r="K38" s="6" t="n">
-        <v>45898</v>
+        <v>45889</v>
       </c>
       <c r="L38" s="4" t="n">
-        <v>298</v>
+        <v>307</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>PROD-004302</t>
+          <t>PROD-001053</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
@@ -4081,30 +4081,30 @@
         </is>
       </c>
       <c r="C39" s="5" t="n">
-        <v>4302</v>
+        <v>1053</v>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>24056829962</t>
+          <t>28168505423</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
         <is>
-          <t>DELT</t>
+          <t>ÉPSI</t>
         </is>
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t>RC PROFISSIONAL</t>
+          <t>RESIDENCIAL</t>
         </is>
       </c>
       <c r="G39" s="5" t="inlineStr">
         <is>
-          <t>PREVIDÊNCIA</t>
+          <t>SAÚDE</t>
         </is>
       </c>
       <c r="H39" s="5" t="n">
-        <v>1228354</v>
+        <v>7743856</v>
       </c>
       <c r="I39" s="5" t="inlineStr">
         <is>
@@ -4112,19 +4112,19 @@
         </is>
       </c>
       <c r="J39" s="7" t="n">
-        <v>45534</v>
+        <v>45525</v>
       </c>
       <c r="K39" s="7" t="n">
-        <v>45899</v>
+        <v>45890</v>
       </c>
       <c r="L39" s="5" t="n">
-        <v>297</v>
+        <v>306</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>PROD-001086</t>
+          <t>PROD-004689</t>
         </is>
       </c>
       <c r="B40" s="4" t="inlineStr">
@@ -4133,30 +4133,30 @@
         </is>
       </c>
       <c r="C40" s="4" t="n">
-        <v>1086</v>
+        <v>4689</v>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>04091570184</t>
+          <t>07596599920</t>
         </is>
       </c>
       <c r="E40" s="4" t="inlineStr">
         <is>
-          <t>ÉPSI</t>
+          <t>DELT</t>
         </is>
       </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
-          <t>AUTOMÓVEL</t>
+          <t>RESIDENCIAL</t>
         </is>
       </c>
       <c r="G40" s="4" t="inlineStr">
         <is>
-          <t>PATRIMONIAL</t>
+          <t>VIAGEM</t>
         </is>
       </c>
       <c r="H40" s="4" t="n">
-        <v>3792503</v>
+        <v>2273776</v>
       </c>
       <c r="I40" s="4" t="inlineStr">
         <is>
@@ -4164,19 +4164,19 @@
         </is>
       </c>
       <c r="J40" s="6" t="n">
-        <v>45534</v>
+        <v>45531</v>
       </c>
       <c r="K40" s="6" t="n">
-        <v>45899</v>
+        <v>45896</v>
       </c>
       <c r="L40" s="4" t="n">
-        <v>297</v>
+        <v>300</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>PROD-001848</t>
+          <t>PROD-000373</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
@@ -4185,21 +4185,21 @@
         </is>
       </c>
       <c r="C41" s="5" t="n">
-        <v>1848</v>
+        <v>373</v>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>54522675289</t>
+          <t>93990916998</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
         <is>
-          <t>DELT</t>
+          <t>BETA</t>
         </is>
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
-          <t>EQUIPAMENTOS</t>
+          <t>VIAGEM</t>
         </is>
       </c>
       <c r="G41" s="5" t="inlineStr">
@@ -4208,7 +4208,7 @@
         </is>
       </c>
       <c r="H41" s="5" t="n">
-        <v>4792077</v>
+        <v>6075106</v>
       </c>
       <c r="I41" s="5" t="inlineStr">
         <is>
@@ -4216,19 +4216,19 @@
         </is>
       </c>
       <c r="J41" s="7" t="n">
-        <v>45538</v>
+        <v>45837</v>
       </c>
       <c r="K41" s="7" t="n">
-        <v>45903</v>
+        <v>45898</v>
       </c>
       <c r="L41" s="5" t="n">
-        <v>293</v>
+        <v>298</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>PROD-003284</t>
+          <t>PROD-004002</t>
         </is>
       </c>
       <c r="B42" s="4" t="inlineStr">
@@ -4237,16 +4237,16 @@
         </is>
       </c>
       <c r="C42" s="4" t="n">
-        <v>3284</v>
+        <v>4002</v>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>27238046827</t>
+          <t>66383615171</t>
         </is>
       </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t>ÉPSI</t>
+          <t>DELT</t>
         </is>
       </c>
       <c r="F42" s="4" t="inlineStr">
@@ -4256,11 +4256,11 @@
       </c>
       <c r="G42" s="4" t="inlineStr">
         <is>
-          <t>AUTO</t>
+          <t>PREVIDÊNCIA</t>
         </is>
       </c>
       <c r="H42" s="4" t="n">
-        <v>7071466</v>
+        <v>1228354</v>
       </c>
       <c r="I42" s="4" t="inlineStr">
         <is>
@@ -4268,19 +4268,19 @@
         </is>
       </c>
       <c r="J42" s="6" t="n">
-        <v>45541</v>
+        <v>45534</v>
       </c>
       <c r="K42" s="6" t="n">
-        <v>45906</v>
+        <v>45899</v>
       </c>
       <c r="L42" s="4" t="n">
-        <v>290</v>
+        <v>297</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>PROD-000511</t>
+          <t>PROD-000786</t>
         </is>
       </c>
       <c r="B43" s="5" t="inlineStr">
@@ -4289,16 +4289,16 @@
         </is>
       </c>
       <c r="C43" s="5" t="n">
-        <v>511</v>
+        <v>786</v>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>42836440892</t>
+          <t>54451895202</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
         <is>
-          <t>ALFA</t>
+          <t>ÉPSI</t>
         </is>
       </c>
       <c r="F43" s="5" t="inlineStr">
@@ -4308,11 +4308,11 @@
       </c>
       <c r="G43" s="5" t="inlineStr">
         <is>
-          <t>SAÚDE</t>
+          <t>PATRIMONIAL</t>
         </is>
       </c>
       <c r="H43" s="5" t="n">
-        <v>8891729</v>
+        <v>3792503</v>
       </c>
       <c r="I43" s="5" t="inlineStr">
         <is>
@@ -4320,19 +4320,19 @@
         </is>
       </c>
       <c r="J43" s="7" t="n">
-        <v>45546</v>
+        <v>45534</v>
       </c>
       <c r="K43" s="7" t="n">
-        <v>45911</v>
+        <v>45899</v>
       </c>
       <c r="L43" s="5" t="n">
-        <v>285</v>
+        <v>297</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>PROD-002693</t>
+          <t>PROD-002984</t>
         </is>
       </c>
       <c r="B44" s="4" t="inlineStr">
@@ -4341,30 +4341,30 @@
         </is>
       </c>
       <c r="C44" s="4" t="n">
-        <v>2693</v>
+        <v>2984</v>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>42626551104</t>
+          <t>64842294057</t>
         </is>
       </c>
       <c r="E44" s="4" t="inlineStr">
         <is>
-          <t>ZETA</t>
+          <t>ÉPSI</t>
         </is>
       </c>
       <c r="F44" s="4" t="inlineStr">
         <is>
-          <t>RESIDENCIAL</t>
+          <t>RC PROFISSIONAL</t>
         </is>
       </c>
       <c r="G44" s="4" t="inlineStr">
         <is>
-          <t>PATRIMONIAL</t>
+          <t>AUTO</t>
         </is>
       </c>
       <c r="H44" s="4" t="n">
-        <v>5522997</v>
+        <v>7071466</v>
       </c>
       <c r="I44" s="4" t="inlineStr">
         <is>
@@ -4372,19 +4372,19 @@
         </is>
       </c>
       <c r="J44" s="6" t="n">
-        <v>45547</v>
+        <v>45541</v>
       </c>
       <c r="K44" s="6" t="n">
-        <v>45912</v>
+        <v>45906</v>
       </c>
       <c r="L44" s="4" t="n">
-        <v>284</v>
+        <v>290</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>PROD-000290</t>
+          <t>PROD-000211</t>
         </is>
       </c>
       <c r="B45" s="5" t="inlineStr">
@@ -4393,30 +4393,30 @@
         </is>
       </c>
       <c r="C45" s="5" t="n">
-        <v>290</v>
+        <v>211</v>
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>84511544796</t>
+          <t>32898614341</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
         <is>
-          <t>GAMA</t>
+          <t>ALFA</t>
         </is>
       </c>
       <c r="F45" s="5" t="inlineStr">
         <is>
-          <t>VIAGEM</t>
+          <t>AUTOMÓVEL</t>
         </is>
       </c>
       <c r="G45" s="5" t="inlineStr">
         <is>
-          <t>AUTO</t>
+          <t>SAÚDE</t>
         </is>
       </c>
       <c r="H45" s="5" t="n">
-        <v>4843324</v>
+        <v>8891729</v>
       </c>
       <c r="I45" s="5" t="inlineStr">
         <is>
@@ -4424,19 +4424,19 @@
         </is>
       </c>
       <c r="J45" s="7" t="n">
-        <v>45885</v>
+        <v>45546</v>
       </c>
       <c r="K45" s="7" t="n">
-        <v>45916</v>
+        <v>45911</v>
       </c>
       <c r="L45" s="5" t="n">
-        <v>280</v>
+        <v>285</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>PROD-000248</t>
+          <t>PROD-002393</t>
         </is>
       </c>
       <c r="B46" s="4" t="inlineStr">
@@ -4445,30 +4445,30 @@
         </is>
       </c>
       <c r="C46" s="4" t="n">
-        <v>248</v>
+        <v>2393</v>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>78292216995</t>
+          <t>62713611155</t>
         </is>
       </c>
       <c r="E46" s="4" t="inlineStr">
         <is>
-          <t>GAMA</t>
+          <t>ZETA</t>
         </is>
       </c>
       <c r="F46" s="4" t="inlineStr">
         <is>
-          <t>EMPRESARIAL</t>
+          <t>RESIDENCIAL</t>
         </is>
       </c>
       <c r="G46" s="4" t="inlineStr">
         <is>
-          <t>RC</t>
+          <t>PATRIMONIAL</t>
         </is>
       </c>
       <c r="H46" s="4" t="n">
-        <v>2785378</v>
+        <v>5522997</v>
       </c>
       <c r="I46" s="4" t="inlineStr">
         <is>
@@ -4476,19 +4476,19 @@
         </is>
       </c>
       <c r="J46" s="6" t="n">
-        <v>45552</v>
+        <v>45547</v>
       </c>
       <c r="K46" s="6" t="n">
-        <v>45917</v>
+        <v>45912</v>
       </c>
       <c r="L46" s="4" t="n">
-        <v>279</v>
+        <v>284</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>PROD-000445</t>
+          <t>PROD-000145</t>
         </is>
       </c>
       <c r="B47" s="5" t="inlineStr">
@@ -4497,11 +4497,11 @@
         </is>
       </c>
       <c r="C47" s="5" t="n">
-        <v>445</v>
+        <v>145</v>
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>52677223306</t>
+          <t>47284639208</t>
         </is>
       </c>
       <c r="E47" s="5" t="inlineStr">
@@ -4540,7 +4540,7 @@
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>PROD-001210</t>
+          <t>PROD-000910</t>
         </is>
       </c>
       <c r="B48" s="4" t="inlineStr">
@@ -4549,11 +4549,11 @@
         </is>
       </c>
       <c r="C48" s="4" t="n">
-        <v>1210</v>
+        <v>910</v>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>05415667652</t>
+          <t>08635365419</t>
         </is>
       </c>
       <c r="E48" s="4" t="inlineStr">
@@ -4592,7 +4592,7 @@
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>PROD-000308</t>
+          <t>PROD-002330</t>
         </is>
       </c>
       <c r="B49" s="5" t="inlineStr">
@@ -4601,16 +4601,16 @@
         </is>
       </c>
       <c r="C49" s="5" t="n">
-        <v>308</v>
+        <v>2330</v>
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>64794738646</t>
+          <t>49588039551</t>
         </is>
       </c>
       <c r="E49" s="5" t="inlineStr">
         <is>
-          <t>ETA</t>
+          <t>TETA</t>
         </is>
       </c>
       <c r="F49" s="5" t="inlineStr">
@@ -4620,11 +4620,11 @@
       </c>
       <c r="G49" s="5" t="inlineStr">
         <is>
-          <t>SAÚDE</t>
+          <t>AUTO</t>
         </is>
       </c>
       <c r="H49" s="5" t="n">
-        <v>1958982</v>
+        <v>8175107</v>
       </c>
       <c r="I49" s="5" t="inlineStr">
         <is>
@@ -4632,19 +4632,19 @@
         </is>
       </c>
       <c r="J49" s="7" t="n">
-        <v>45902</v>
+        <v>45852</v>
       </c>
       <c r="K49" s="7" t="n">
-        <v>45932</v>
+        <v>45944</v>
       </c>
       <c r="L49" s="5" t="n">
-        <v>264</v>
+        <v>252</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>PROD-002630</t>
+          <t>PROD-002008</t>
         </is>
       </c>
       <c r="B50" s="4" t="inlineStr">
@@ -4653,21 +4653,21 @@
         </is>
       </c>
       <c r="C50" s="4" t="n">
-        <v>2630</v>
+        <v>2008</v>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>75003691559</t>
+          <t>77547812914</t>
         </is>
       </c>
       <c r="E50" s="4" t="inlineStr">
         <is>
-          <t>TETA</t>
+          <t>DELT</t>
         </is>
       </c>
       <c r="F50" s="4" t="inlineStr">
         <is>
-          <t>VIAGEM</t>
+          <t>RESIDENCIAL</t>
         </is>
       </c>
       <c r="G50" s="4" t="inlineStr">
@@ -4676,7 +4676,7 @@
         </is>
       </c>
       <c r="H50" s="4" t="n">
-        <v>8175107</v>
+        <v>1513731</v>
       </c>
       <c r="I50" s="4" t="inlineStr">
         <is>
@@ -4684,19 +4684,19 @@
         </is>
       </c>
       <c r="J50" s="6" t="n">
-        <v>45852</v>
+        <v>45582</v>
       </c>
       <c r="K50" s="6" t="n">
-        <v>45944</v>
+        <v>45947</v>
       </c>
       <c r="L50" s="4" t="n">
-        <v>252</v>
+        <v>249</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>PROD-002308</t>
+          <t>PROD-000987</t>
         </is>
       </c>
       <c r="B51" s="5" t="inlineStr">
@@ -4705,11 +4705,11 @@
         </is>
       </c>
       <c r="C51" s="5" t="n">
-        <v>2308</v>
+        <v>987</v>
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>49947174648</t>
+          <t>99552717744</t>
         </is>
       </c>
       <c r="E51" s="5" t="inlineStr">
@@ -4719,16 +4719,16 @@
       </c>
       <c r="F51" s="5" t="inlineStr">
         <is>
-          <t>RESIDENCIAL</t>
+          <t>VIAGEM</t>
         </is>
       </c>
       <c r="G51" s="5" t="inlineStr">
         <is>
-          <t>AUTO</t>
+          <t>PREVIDÊNCIA</t>
         </is>
       </c>
       <c r="H51" s="5" t="n">
-        <v>1513731</v>
+        <v>1898452</v>
       </c>
       <c r="I51" s="5" t="inlineStr">
         <is>
@@ -4736,19 +4736,19 @@
         </is>
       </c>
       <c r="J51" s="7" t="n">
-        <v>45582</v>
+        <v>45893</v>
       </c>
       <c r="K51" s="7" t="n">
-        <v>45947</v>
+        <v>45954</v>
       </c>
       <c r="L51" s="5" t="n">
-        <v>249</v>
+        <v>242</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>PROD-004692</t>
+          <t>PROD-004392</t>
         </is>
       </c>
       <c r="B52" s="4" t="inlineStr">
@@ -4757,11 +4757,11 @@
         </is>
       </c>
       <c r="C52" s="4" t="n">
-        <v>4692</v>
+        <v>4392</v>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>35158807053</t>
+          <t>42579913662</t>
         </is>
       </c>
       <c r="E52" s="4" t="inlineStr">
@@ -4800,7 +4800,7 @@
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t>PROD-003201</t>
+          <t>PROD-000708</t>
         </is>
       </c>
       <c r="B53" s="5" t="inlineStr">
@@ -4809,11 +4809,11 @@
         </is>
       </c>
       <c r="C53" s="5" t="n">
-        <v>3201</v>
+        <v>708</v>
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>04899642353</t>
+          <t>71902294131</t>
         </is>
       </c>
       <c r="E53" s="5" t="inlineStr">
@@ -4823,7 +4823,7 @@
       </c>
       <c r="F53" s="5" t="inlineStr">
         <is>
-          <t>EQUIPAMENTOS</t>
+          <t>RESIDENCIAL</t>
         </is>
       </c>
       <c r="G53" s="5" t="inlineStr">
@@ -4832,7 +4832,7 @@
         </is>
       </c>
       <c r="H53" s="5" t="n">
-        <v>2788773</v>
+        <v>8572545</v>
       </c>
       <c r="I53" s="5" t="inlineStr">
         <is>
@@ -4840,19 +4840,19 @@
         </is>
       </c>
       <c r="J53" s="7" t="n">
-        <v>45986</v>
+        <v>45594</v>
       </c>
       <c r="K53" s="7" t="n">
-        <v>45956</v>
+        <v>45959</v>
       </c>
       <c r="L53" s="5" t="n">
-        <v>240</v>
+        <v>237</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="4" t="inlineStr">
         <is>
-          <t>PROD-001008</t>
+          <t>PROD-000822</t>
         </is>
       </c>
       <c r="B54" s="4" t="inlineStr">
@@ -4861,11 +4861,11 @@
         </is>
       </c>
       <c r="C54" s="4" t="n">
-        <v>1008</v>
+        <v>822</v>
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>54544432830</t>
+          <t>11266912153</t>
         </is>
       </c>
       <c r="E54" s="4" t="inlineStr">
@@ -4875,16 +4875,16 @@
       </c>
       <c r="F54" s="4" t="inlineStr">
         <is>
-          <t>RESIDENCIAL</t>
+          <t>VIAGEM</t>
         </is>
       </c>
       <c r="G54" s="4" t="inlineStr">
         <is>
-          <t>VIAGEM</t>
+          <t>PATRIMONIAL</t>
         </is>
       </c>
       <c r="H54" s="4" t="n">
-        <v>8572545</v>
+        <v>7629911</v>
       </c>
       <c r="I54" s="4" t="inlineStr">
         <is>
@@ -4892,7 +4892,7 @@
         </is>
       </c>
       <c r="J54" s="6" t="n">
-        <v>45594</v>
+        <v>45898</v>
       </c>
       <c r="K54" s="6" t="n">
         <v>45959</v>
@@ -4904,7 +4904,7 @@
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t>PROD-001122</t>
+          <t>PROD-004530</t>
         </is>
       </c>
       <c r="B55" s="5" t="inlineStr">
@@ -4913,30 +4913,30 @@
         </is>
       </c>
       <c r="C55" s="5" t="n">
-        <v>1122</v>
+        <v>4530</v>
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>57027937145</t>
+          <t>26984858333</t>
         </is>
       </c>
       <c r="E55" s="5" t="inlineStr">
         <is>
-          <t>DELT</t>
+          <t>TETA</t>
         </is>
       </c>
       <c r="F55" s="5" t="inlineStr">
         <is>
-          <t>VIAGEM</t>
+          <t>EMPRESARIAL</t>
         </is>
       </c>
       <c r="G55" s="5" t="inlineStr">
         <is>
-          <t>PATRIMONIAL</t>
+          <t>SAÚDE</t>
         </is>
       </c>
       <c r="H55" s="5" t="n">
-        <v>7629911</v>
+        <v>9290143</v>
       </c>
       <c r="I55" s="5" t="inlineStr">
         <is>
@@ -4944,19 +4944,19 @@
         </is>
       </c>
       <c r="J55" s="7" t="n">
-        <v>45898</v>
+        <v>45605</v>
       </c>
       <c r="K55" s="7" t="n">
-        <v>45959</v>
+        <v>45970</v>
       </c>
       <c r="L55" s="5" t="n">
-        <v>237</v>
+        <v>226</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="4" t="inlineStr">
         <is>
-          <t>PROD-000254</t>
+          <t>PROD-003458</t>
         </is>
       </c>
       <c r="B56" s="4" t="inlineStr">
@@ -4965,30 +4965,30 @@
         </is>
       </c>
       <c r="C56" s="4" t="n">
-        <v>254</v>
+        <v>3458</v>
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>53926442209</t>
+          <t>75326973112</t>
         </is>
       </c>
       <c r="E56" s="4" t="inlineStr">
         <is>
-          <t>GAMA</t>
+          <t>ZETA</t>
         </is>
       </c>
       <c r="F56" s="4" t="inlineStr">
         <is>
-          <t>RESIDENCIAL</t>
+          <t>EMPRESARIAL</t>
         </is>
       </c>
       <c r="G56" s="4" t="inlineStr">
         <is>
-          <t>PATRIMONIAL</t>
+          <t>AUTO</t>
         </is>
       </c>
       <c r="H56" s="4" t="n">
-        <v>5258144</v>
+        <v>2590365</v>
       </c>
       <c r="I56" s="4" t="inlineStr">
         <is>
@@ -4996,19 +4996,19 @@
         </is>
       </c>
       <c r="J56" s="6" t="n">
-        <v>45597</v>
+        <v>45605</v>
       </c>
       <c r="K56" s="6" t="n">
-        <v>45962</v>
+        <v>45970</v>
       </c>
       <c r="L56" s="4" t="n">
-        <v>234</v>
+        <v>226</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="5" t="inlineStr">
         <is>
-          <t>PROD-003758</t>
+          <t>PROD-001279</t>
         </is>
       </c>
       <c r="B57" s="5" t="inlineStr">
@@ -5017,30 +5017,30 @@
         </is>
       </c>
       <c r="C57" s="5" t="n">
-        <v>3758</v>
+        <v>1279</v>
       </c>
       <c r="D57" s="5" t="inlineStr">
         <is>
-          <t>43280634615</t>
+          <t>37693898331</t>
         </is>
       </c>
       <c r="E57" s="5" t="inlineStr">
         <is>
-          <t>ZETA</t>
+          <t>TETA</t>
         </is>
       </c>
       <c r="F57" s="5" t="inlineStr">
         <is>
-          <t>EMPRESARIAL</t>
+          <t>VIAGEM</t>
         </is>
       </c>
       <c r="G57" s="5" t="inlineStr">
         <is>
-          <t>AUTO</t>
+          <t>RC</t>
         </is>
       </c>
       <c r="H57" s="5" t="n">
-        <v>2590365</v>
+        <v>5119761</v>
       </c>
       <c r="I57" s="5" t="inlineStr">
         <is>
@@ -5048,19 +5048,19 @@
         </is>
       </c>
       <c r="J57" s="7" t="n">
-        <v>45605</v>
+        <v>46001</v>
       </c>
       <c r="K57" s="7" t="n">
-        <v>45970</v>
+        <v>45971</v>
       </c>
       <c r="L57" s="5" t="n">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="4" t="inlineStr">
         <is>
-          <t>PROD-003450</t>
+          <t>PROD-002500</t>
         </is>
       </c>
       <c r="B58" s="4" t="inlineStr">
@@ -5069,30 +5069,30 @@
         </is>
       </c>
       <c r="C58" s="4" t="n">
-        <v>3450</v>
+        <v>2500</v>
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>59059929378</t>
+          <t>45868501429</t>
         </is>
       </c>
       <c r="E58" s="4" t="inlineStr">
         <is>
-          <t>GAMA</t>
+          <t>ETA</t>
         </is>
       </c>
       <c r="F58" s="4" t="inlineStr">
         <is>
-          <t>AUTOMÓVEL</t>
+          <t>VIAGEM</t>
         </is>
       </c>
       <c r="G58" s="4" t="inlineStr">
         <is>
-          <t>RC</t>
+          <t>SAÚDE</t>
         </is>
       </c>
       <c r="H58" s="4" t="n">
-        <v>5220854</v>
+        <v>7519642</v>
       </c>
       <c r="I58" s="4" t="inlineStr">
         <is>
@@ -5100,7 +5100,7 @@
         </is>
       </c>
       <c r="J58" s="6" t="n">
-        <v>45610</v>
+        <v>45914</v>
       </c>
       <c r="K58" s="6" t="n">
         <v>45975</v>
@@ -5112,7 +5112,7 @@
     <row r="59">
       <c r="A59" s="5" t="inlineStr">
         <is>
-          <t>PROD-002800</t>
+          <t>PROD-003150</t>
         </is>
       </c>
       <c r="B59" s="5" t="inlineStr">
@@ -5121,30 +5121,30 @@
         </is>
       </c>
       <c r="C59" s="5" t="n">
-        <v>2800</v>
+        <v>3150</v>
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t>04633312797</t>
+          <t>77584161692</t>
         </is>
       </c>
       <c r="E59" s="5" t="inlineStr">
         <is>
-          <t>ETA</t>
+          <t>GAMA</t>
         </is>
       </c>
       <c r="F59" s="5" t="inlineStr">
         <is>
-          <t>VIAGEM</t>
+          <t>AUTOMÓVEL</t>
         </is>
       </c>
       <c r="G59" s="5" t="inlineStr">
         <is>
-          <t>SAÚDE</t>
+          <t>RC</t>
         </is>
       </c>
       <c r="H59" s="5" t="n">
-        <v>7519642</v>
+        <v>5220854</v>
       </c>
       <c r="I59" s="5" t="inlineStr">
         <is>
@@ -5152,7 +5152,7 @@
         </is>
       </c>
       <c r="J59" s="7" t="n">
-        <v>45914</v>
+        <v>45610</v>
       </c>
       <c r="K59" s="7" t="n">
         <v>45975</v>
@@ -5164,7 +5164,7 @@
     <row r="60">
       <c r="A60" s="4" t="inlineStr">
         <is>
-          <t>PROD-001033</t>
+          <t>PROD-004552</t>
         </is>
       </c>
       <c r="B60" s="4" t="inlineStr">
@@ -5173,11 +5173,11 @@
         </is>
       </c>
       <c r="C60" s="4" t="n">
-        <v>1033</v>
+        <v>4552</v>
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>37923747407</t>
+          <t>06724004991</t>
         </is>
       </c>
       <c r="E60" s="4" t="inlineStr">
@@ -5187,16 +5187,16 @@
       </c>
       <c r="F60" s="4" t="inlineStr">
         <is>
-          <t>EMPRESARIAL</t>
+          <t>VIAGEM</t>
         </is>
       </c>
       <c r="G60" s="4" t="inlineStr">
         <is>
-          <t>VIDA</t>
+          <t>AUTO</t>
         </is>
       </c>
       <c r="H60" s="4" t="n">
-        <v>6382929</v>
+        <v>4397520</v>
       </c>
       <c r="I60" s="4" t="inlineStr">
         <is>
@@ -5204,19 +5204,19 @@
         </is>
       </c>
       <c r="J60" s="6" t="n">
-        <v>45619</v>
+        <v>45885</v>
       </c>
       <c r="K60" s="6" t="n">
-        <v>45984</v>
+        <v>45977</v>
       </c>
       <c r="L60" s="4" t="n">
-        <v>212</v>
+        <v>219</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="5" t="inlineStr">
         <is>
-          <t>PROD-000537</t>
+          <t>PROD-004572</t>
         </is>
       </c>
       <c r="B61" s="5" t="inlineStr">
@@ -5225,30 +5225,30 @@
         </is>
       </c>
       <c r="C61" s="5" t="n">
-        <v>537</v>
+        <v>4572</v>
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>10433218196</t>
+          <t>89137189490</t>
         </is>
       </c>
       <c r="E61" s="5" t="inlineStr">
         <is>
-          <t>ALFA</t>
+          <t>TETA</t>
         </is>
       </c>
       <c r="F61" s="5" t="inlineStr">
         <is>
-          <t>AUTOMÓVEL</t>
+          <t>EQUIPAMENTOS</t>
         </is>
       </c>
       <c r="G61" s="5" t="inlineStr">
         <is>
-          <t>SAÚDE</t>
+          <t>RC</t>
         </is>
       </c>
       <c r="H61" s="5" t="n">
-        <v>5723052</v>
+        <v>2638758</v>
       </c>
       <c r="I61" s="5" t="inlineStr">
         <is>
@@ -5256,19 +5256,19 @@
         </is>
       </c>
       <c r="J61" s="7" t="n">
-        <v>45621</v>
+        <v>45618</v>
       </c>
       <c r="K61" s="7" t="n">
-        <v>45986</v>
+        <v>45983</v>
       </c>
       <c r="L61" s="5" t="n">
-        <v>210</v>
+        <v>213</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="4" t="inlineStr">
         <is>
-          <t>PROD-000417</t>
+          <t>PROD-000733</t>
         </is>
       </c>
       <c r="B62" s="4" t="inlineStr">
@@ -5277,30 +5277,30 @@
         </is>
       </c>
       <c r="C62" s="4" t="n">
-        <v>417</v>
+        <v>733</v>
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>20644742123</t>
+          <t>29218515691</t>
         </is>
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
-          <t>GAMA</t>
+          <t>ETA</t>
         </is>
       </c>
       <c r="F62" s="4" t="inlineStr">
         <is>
-          <t>RC PROFISSIONAL</t>
+          <t>EMPRESARIAL</t>
         </is>
       </c>
       <c r="G62" s="4" t="inlineStr">
         <is>
-          <t>RC</t>
+          <t>VIDA</t>
         </is>
       </c>
       <c r="H62" s="4" t="n">
-        <v>6018860</v>
+        <v>6382929</v>
       </c>
       <c r="I62" s="4" t="inlineStr">
         <is>
@@ -5308,19 +5308,19 @@
         </is>
       </c>
       <c r="J62" s="6" t="n">
-        <v>45622</v>
+        <v>45619</v>
       </c>
       <c r="K62" s="6" t="n">
-        <v>45987</v>
+        <v>45984</v>
       </c>
       <c r="L62" s="4" t="n">
-        <v>209</v>
+        <v>212</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="5" t="inlineStr">
         <is>
-          <t>PROD-002801</t>
+          <t>PROD-000237</t>
         </is>
       </c>
       <c r="B63" s="5" t="inlineStr">
@@ -5329,30 +5329,30 @@
         </is>
       </c>
       <c r="C63" s="5" t="n">
-        <v>2801</v>
+        <v>237</v>
       </c>
       <c r="D63" s="5" t="inlineStr">
         <is>
-          <t>04633312797</t>
+          <t>99042102027</t>
         </is>
       </c>
       <c r="E63" s="5" t="inlineStr">
         <is>
-          <t>GAMA</t>
+          <t>ALFA</t>
         </is>
       </c>
       <c r="F63" s="5" t="inlineStr">
         <is>
-          <t>VIAGEM</t>
+          <t>AUTOMÓVEL</t>
         </is>
       </c>
       <c r="G63" s="5" t="inlineStr">
         <is>
-          <t>AUTO</t>
+          <t>SAÚDE</t>
         </is>
       </c>
       <c r="H63" s="5" t="n">
-        <v>3288452</v>
+        <v>5723052</v>
       </c>
       <c r="I63" s="5" t="inlineStr">
         <is>
@@ -5360,19 +5360,19 @@
         </is>
       </c>
       <c r="J63" s="7" t="n">
-        <v>45928</v>
+        <v>45621</v>
       </c>
       <c r="K63" s="7" t="n">
-        <v>45989</v>
+        <v>45986</v>
       </c>
       <c r="L63" s="5" t="n">
-        <v>207</v>
+        <v>210</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="4" t="inlineStr">
         <is>
-          <t>PROD-003917</t>
+          <t>PROD-000117</t>
         </is>
       </c>
       <c r="B64" s="4" t="inlineStr">
@@ -5381,30 +5381,30 @@
         </is>
       </c>
       <c r="C64" s="4" t="n">
-        <v>3917</v>
+        <v>117</v>
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>28685289755</t>
+          <t>57905528183</t>
         </is>
       </c>
       <c r="E64" s="4" t="inlineStr">
         <is>
-          <t>BETA</t>
+          <t>GAMA</t>
         </is>
       </c>
       <c r="F64" s="4" t="inlineStr">
         <is>
-          <t>EQUIPAMENTOS</t>
+          <t>RC PROFISSIONAL</t>
         </is>
       </c>
       <c r="G64" s="4" t="inlineStr">
         <is>
-          <t>AUTO</t>
+          <t>RC</t>
         </is>
       </c>
       <c r="H64" s="4" t="n">
-        <v>8281628</v>
+        <v>6018860</v>
       </c>
       <c r="I64" s="4" t="inlineStr">
         <is>
@@ -5412,19 +5412,19 @@
         </is>
       </c>
       <c r="J64" s="6" t="n">
-        <v>45627</v>
+        <v>45622</v>
       </c>
       <c r="K64" s="6" t="n">
-        <v>45992</v>
+        <v>45987</v>
       </c>
       <c r="L64" s="4" t="n">
-        <v>204</v>
+        <v>209</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="5" t="inlineStr">
         <is>
-          <t>PROD-000117</t>
+          <t>PROD-002501</t>
         </is>
       </c>
       <c r="B65" s="5" t="inlineStr">
@@ -5433,30 +5433,30 @@
         </is>
       </c>
       <c r="C65" s="5" t="n">
-        <v>117</v>
+        <v>2501</v>
       </c>
       <c r="D65" s="5" t="inlineStr">
         <is>
-          <t>68486661889</t>
+          <t>45868501429</t>
         </is>
       </c>
       <c r="E65" s="5" t="inlineStr">
         <is>
-          <t>ZETA</t>
+          <t>GAMA</t>
         </is>
       </c>
       <c r="F65" s="5" t="inlineStr">
         <is>
-          <t>RC PROFISSIONAL</t>
+          <t>VIAGEM</t>
         </is>
       </c>
       <c r="G65" s="5" t="inlineStr">
         <is>
-          <t>RC</t>
+          <t>AUTO</t>
         </is>
       </c>
       <c r="H65" s="5" t="n">
-        <v>3374338</v>
+        <v>3288452</v>
       </c>
       <c r="I65" s="5" t="inlineStr">
         <is>
@@ -5464,19 +5464,19 @@
         </is>
       </c>
       <c r="J65" s="7" t="n">
-        <v>45631</v>
+        <v>45928</v>
       </c>
       <c r="K65" s="7" t="n">
-        <v>45996</v>
+        <v>45989</v>
       </c>
       <c r="L65" s="5" t="n">
-        <v>200</v>
+        <v>207</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="4" t="inlineStr">
         <is>
-          <t>PROD-002053</t>
+          <t>PROD-003175</t>
         </is>
       </c>
       <c r="B66" s="4" t="inlineStr">
@@ -5485,16 +5485,16 @@
         </is>
       </c>
       <c r="C66" s="4" t="n">
-        <v>2053</v>
+        <v>3175</v>
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>65375564641</t>
+          <t>49947174648</t>
         </is>
       </c>
       <c r="E66" s="4" t="inlineStr">
         <is>
-          <t>ETA</t>
+          <t>BETA</t>
         </is>
       </c>
       <c r="F66" s="4" t="inlineStr">
@@ -5504,11 +5504,11 @@
       </c>
       <c r="G66" s="4" t="inlineStr">
         <is>
-          <t>RC</t>
+          <t>VIDA</t>
         </is>
       </c>
       <c r="H66" s="4" t="n">
-        <v>5778306</v>
+        <v>54482732025</v>
       </c>
       <c r="I66" s="4" t="inlineStr">
         <is>
@@ -5516,19 +5516,19 @@
         </is>
       </c>
       <c r="J66" s="6" t="n">
-        <v>45637</v>
+        <v>46019</v>
       </c>
       <c r="K66" s="6" t="n">
-        <v>46002</v>
+        <v>45989</v>
       </c>
       <c r="L66" s="4" t="n">
-        <v>194</v>
+        <v>207</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="5" t="inlineStr">
         <is>
-          <t>PROD-004777</t>
+          <t>PROD-003617</t>
         </is>
       </c>
       <c r="B67" s="5" t="inlineStr">
@@ -5537,30 +5537,30 @@
         </is>
       </c>
       <c r="C67" s="5" t="n">
-        <v>4777</v>
+        <v>3617</v>
       </c>
       <c r="D67" s="5" t="inlineStr">
         <is>
-          <t>89994043898</t>
+          <t>01398373540</t>
         </is>
       </c>
       <c r="E67" s="5" t="inlineStr">
         <is>
-          <t>ÉPSI</t>
+          <t>BETA</t>
         </is>
       </c>
       <c r="F67" s="5" t="inlineStr">
         <is>
-          <t>AUTOMÓVEL</t>
+          <t>EQUIPAMENTOS</t>
         </is>
       </c>
       <c r="G67" s="5" t="inlineStr">
         <is>
-          <t>RC</t>
+          <t>AUTO</t>
         </is>
       </c>
       <c r="H67" s="5" t="n">
-        <v>7290592</v>
+        <v>8281628</v>
       </c>
       <c r="I67" s="5" t="inlineStr">
         <is>
@@ -5568,19 +5568,19 @@
         </is>
       </c>
       <c r="J67" s="7" t="n">
-        <v>45641</v>
+        <v>45627</v>
       </c>
       <c r="K67" s="7" t="n">
-        <v>46006</v>
+        <v>45992</v>
       </c>
       <c r="L67" s="5" t="n">
-        <v>190</v>
+        <v>204</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="4" t="inlineStr">
         <is>
-          <t>PROD-001842</t>
+          <t>PROD-001753</t>
         </is>
       </c>
       <c r="B68" s="4" t="inlineStr">
@@ -5589,16 +5589,16 @@
         </is>
       </c>
       <c r="C68" s="4" t="n">
-        <v>1842</v>
+        <v>1753</v>
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>89994043898</t>
+          <t>20417929111</t>
         </is>
       </c>
       <c r="E68" s="4" t="inlineStr">
         <is>
-          <t>ÉPSI</t>
+          <t>ETA</t>
         </is>
       </c>
       <c r="F68" s="4" t="inlineStr">
@@ -5612,7 +5612,7 @@
         </is>
       </c>
       <c r="H68" s="4" t="n">
-        <v>7290592</v>
+        <v>5778306</v>
       </c>
       <c r="I68" s="4" t="inlineStr">
         <is>
@@ -5620,19 +5620,19 @@
         </is>
       </c>
       <c r="J68" s="6" t="n">
-        <v>45641</v>
+        <v>45637</v>
       </c>
       <c r="K68" s="6" t="n">
-        <v>46006</v>
+        <v>46002</v>
       </c>
       <c r="L68" s="4" t="n">
-        <v>190</v>
+        <v>194</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="5" t="inlineStr">
         <is>
-          <t>PROD-003206</t>
+          <t>PROD-001542</t>
         </is>
       </c>
       <c r="B69" s="5" t="inlineStr">
@@ -5641,30 +5641,30 @@
         </is>
       </c>
       <c r="C69" s="5" t="n">
-        <v>3206</v>
+        <v>1542</v>
       </c>
       <c r="D69" s="5" t="inlineStr">
         <is>
-          <t>40640909743</t>
+          <t>96561014388</t>
         </is>
       </c>
       <c r="E69" s="5" t="inlineStr">
         <is>
-          <t>ZETA</t>
+          <t>ÉPSI</t>
         </is>
       </c>
       <c r="F69" s="5" t="inlineStr">
         <is>
-          <t>RC PROFISSIONAL</t>
+          <t>AUTOMÓVEL</t>
         </is>
       </c>
       <c r="G69" s="5" t="inlineStr">
         <is>
-          <t>AUTO</t>
+          <t>RC</t>
         </is>
       </c>
       <c r="H69" s="5" t="n">
-        <v>2216000</v>
+        <v>7290592</v>
       </c>
       <c r="I69" s="5" t="inlineStr">
         <is>
@@ -5672,19 +5672,19 @@
         </is>
       </c>
       <c r="J69" s="7" t="n">
-        <v>45647</v>
+        <v>45641</v>
       </c>
       <c r="K69" s="7" t="n">
-        <v>46012</v>
+        <v>46006</v>
       </c>
       <c r="L69" s="5" t="n">
-        <v>184</v>
+        <v>190</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="4" t="inlineStr">
         <is>
-          <t>PROD-003791</t>
+          <t>PROD-002906</t>
         </is>
       </c>
       <c r="B70" s="4" t="inlineStr">
@@ -5693,30 +5693,30 @@
         </is>
       </c>
       <c r="C70" s="4" t="n">
-        <v>3791</v>
+        <v>2906</v>
       </c>
       <c r="D70" s="4" t="inlineStr">
         <is>
-          <t>56704310385</t>
+          <t>51820377889</t>
         </is>
       </c>
       <c r="E70" s="4" t="inlineStr">
         <is>
-          <t>BETA</t>
+          <t>ZETA</t>
         </is>
       </c>
       <c r="F70" s="4" t="inlineStr">
         <is>
-          <t>RESIDENCIAL</t>
+          <t>RC PROFISSIONAL</t>
         </is>
       </c>
       <c r="G70" s="4" t="inlineStr">
         <is>
-          <t>VIAGEM</t>
+          <t>AUTO</t>
         </is>
       </c>
       <c r="H70" s="4" t="n">
-        <v>3249784</v>
+        <v>2216000</v>
       </c>
       <c r="I70" s="4" t="inlineStr">
         <is>
@@ -5736,7 +5736,7 @@
     <row r="71">
       <c r="A71" s="5" t="inlineStr">
         <is>
-          <t>PROD-003200</t>
+          <t>PROD-003491</t>
         </is>
       </c>
       <c r="B71" s="5" t="inlineStr">
@@ -5745,30 +5745,30 @@
         </is>
       </c>
       <c r="C71" s="5" t="n">
-        <v>3200</v>
+        <v>3491</v>
       </c>
       <c r="D71" s="5" t="inlineStr">
         <is>
-          <t>42622189092</t>
+          <t>26368970283</t>
         </is>
       </c>
       <c r="E71" s="5" t="inlineStr">
         <is>
-          <t>GAMA</t>
+          <t>BETA</t>
         </is>
       </c>
       <c r="F71" s="5" t="inlineStr">
         <is>
-          <t>EQUIPAMENTOS</t>
+          <t>RESIDENCIAL</t>
         </is>
       </c>
       <c r="G71" s="5" t="inlineStr">
         <is>
-          <t>VIDA</t>
+          <t>VIAGEM</t>
         </is>
       </c>
       <c r="H71" s="5" t="n">
-        <v>4791069</v>
+        <v>3249784</v>
       </c>
       <c r="I71" s="5" t="inlineStr">
         <is>
@@ -5776,19 +5776,19 @@
         </is>
       </c>
       <c r="J71" s="7" t="n">
-        <v>45651</v>
+        <v>45647</v>
       </c>
       <c r="K71" s="7" t="n">
-        <v>46016</v>
+        <v>46012</v>
       </c>
       <c r="L71" s="5" t="n">
-        <v>180</v>
+        <v>184</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="4" t="inlineStr">
         <is>
-          <t>PROD-003474</t>
+          <t>PROD-000023</t>
         </is>
       </c>
       <c r="B72" s="4" t="inlineStr">
@@ -5797,30 +5797,30 @@
         </is>
       </c>
       <c r="C72" s="4" t="n">
-        <v>3474</v>
+        <v>23</v>
       </c>
       <c r="D72" s="4" t="inlineStr">
         <is>
-          <t>57662702895</t>
+          <t>01676184723</t>
         </is>
       </c>
       <c r="E72" s="4" t="inlineStr">
         <is>
-          <t>BETA</t>
+          <t>GAMA</t>
         </is>
       </c>
       <c r="F72" s="4" t="inlineStr">
         <is>
-          <t>AUTOMÓVEL</t>
+          <t>VIAGEM</t>
         </is>
       </c>
       <c r="G72" s="4" t="inlineStr">
         <is>
-          <t>VIDA</t>
+          <t>PREVIDÊNCIA</t>
         </is>
       </c>
       <c r="H72" s="4" t="n">
-        <v>5448273</v>
+        <v>8004579</v>
       </c>
       <c r="I72" s="4" t="inlineStr">
         <is>
@@ -5828,19 +5828,19 @@
         </is>
       </c>
       <c r="J72" s="6" t="n">
-        <v>45654</v>
+        <v>45952</v>
       </c>
       <c r="K72" s="6" t="n">
-        <v>46019</v>
+        <v>46013</v>
       </c>
       <c r="L72" s="4" t="n">
-        <v>177</v>
+        <v>183</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="5" t="inlineStr">
         <is>
-          <t>PROD-004724</t>
+          <t>PROD-002900</t>
         </is>
       </c>
       <c r="B73" s="5" t="inlineStr">
@@ -5849,30 +5849,30 @@
         </is>
       </c>
       <c r="C73" s="5" t="n">
-        <v>4724</v>
+        <v>2900</v>
       </c>
       <c r="D73" s="5" t="inlineStr">
         <is>
-          <t>82974255136</t>
+          <t>57662702895</t>
         </is>
       </c>
       <c r="E73" s="5" t="inlineStr">
         <is>
-          <t>ALFA</t>
+          <t>GAMA</t>
         </is>
       </c>
       <c r="F73" s="5" t="inlineStr">
         <is>
-          <t>RC PROFISSIONAL</t>
+          <t>EQUIPAMENTOS</t>
         </is>
       </c>
       <c r="G73" s="5" t="inlineStr">
         <is>
-          <t>PREVIDÊNCIA</t>
+          <t>VIDA</t>
         </is>
       </c>
       <c r="H73" s="5" t="n">
-        <v>6800654</v>
+        <v>4791069</v>
       </c>
       <c r="I73" s="5" t="inlineStr">
         <is>
@@ -5880,19 +5880,19 @@
         </is>
       </c>
       <c r="J73" s="7" t="n">
-        <v>45657</v>
+        <v>45651</v>
       </c>
       <c r="K73" s="7" t="n">
-        <v>46022</v>
+        <v>46016</v>
       </c>
       <c r="L73" s="5" t="n">
-        <v>174</v>
+        <v>180</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="4" t="inlineStr">
         <is>
-          <t>PROD-000336</t>
+          <t>PROD-003174</t>
         </is>
       </c>
       <c r="B74" s="4" t="inlineStr">
@@ -5901,30 +5901,30 @@
         </is>
       </c>
       <c r="C74" s="4" t="n">
-        <v>336</v>
+        <v>3174</v>
       </c>
       <c r="D74" s="4" t="inlineStr">
         <is>
-          <t>55394237333</t>
+          <t>49947174648</t>
         </is>
       </c>
       <c r="E74" s="4" t="inlineStr">
         <is>
-          <t>ZETA</t>
+          <t>BETA</t>
         </is>
       </c>
       <c r="F74" s="4" t="inlineStr">
         <is>
-          <t>VIAGEM</t>
+          <t>AUTOMÓVEL</t>
         </is>
       </c>
       <c r="G74" s="4" t="inlineStr">
         <is>
-          <t>AUTO</t>
+          <t>VIDA</t>
         </is>
       </c>
       <c r="H74" s="4" t="n">
-        <v>5552948</v>
+        <v>5448273</v>
       </c>
       <c r="I74" s="4" t="inlineStr">
         <is>
@@ -5932,19 +5932,19 @@
         </is>
       </c>
       <c r="J74" s="6" t="n">
-        <v>45962</v>
+        <v>45654</v>
       </c>
       <c r="K74" s="6" t="n">
-        <v>46023</v>
+        <v>46019</v>
       </c>
       <c r="L74" s="4" t="n">
-        <v>173</v>
+        <v>177</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="5" t="inlineStr">
         <is>
-          <t>PROD-002080</t>
+          <t>PROD-004424</t>
         </is>
       </c>
       <c r="B75" s="5" t="inlineStr">
@@ -5953,30 +5953,30 @@
         </is>
       </c>
       <c r="C75" s="5" t="n">
-        <v>2080</v>
+        <v>4424</v>
       </c>
       <c r="D75" s="5" t="inlineStr">
         <is>
-          <t>43757584419</t>
+          <t>52677223306</t>
         </is>
       </c>
       <c r="E75" s="5" t="inlineStr">
         <is>
-          <t>ÉPSI</t>
+          <t>ALFA</t>
         </is>
       </c>
       <c r="F75" s="5" t="inlineStr">
         <is>
-          <t>EQUIPAMENTOS</t>
+          <t>RC PROFISSIONAL</t>
         </is>
       </c>
       <c r="G75" s="5" t="inlineStr">
         <is>
-          <t>PATRIMONIAL</t>
+          <t>PREVIDÊNCIA</t>
         </is>
       </c>
       <c r="H75" s="5" t="n">
-        <v>5166325</v>
+        <v>6800654</v>
       </c>
       <c r="I75" s="5" t="inlineStr">
         <is>
@@ -5984,19 +5984,19 @@
         </is>
       </c>
       <c r="J75" s="7" t="n">
-        <v>45658</v>
+        <v>45657</v>
       </c>
       <c r="K75" s="7" t="n">
-        <v>46023</v>
+        <v>46022</v>
       </c>
       <c r="L75" s="5" t="n">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="4" t="inlineStr">
         <is>
-          <t>PROD-000088</t>
+          <t>PROD-000036</t>
         </is>
       </c>
       <c r="B76" s="4" t="inlineStr">
@@ -6005,30 +6005,30 @@
         </is>
       </c>
       <c r="C76" s="4" t="n">
-        <v>88</v>
+        <v>36</v>
       </c>
       <c r="D76" s="4" t="inlineStr">
         <is>
-          <t>57366096569</t>
+          <t>78078235784</t>
         </is>
       </c>
       <c r="E76" s="4" t="inlineStr">
         <is>
-          <t>ETA</t>
+          <t>ZETA</t>
         </is>
       </c>
       <c r="F76" s="4" t="inlineStr">
         <is>
-          <t>RC PROFISSIONAL</t>
+          <t>VIAGEM</t>
         </is>
       </c>
       <c r="G76" s="4" t="inlineStr">
         <is>
-          <t>VIAGEM</t>
+          <t>AUTO</t>
         </is>
       </c>
       <c r="H76" s="4" t="n">
-        <v>9990249</v>
+        <v>5552948</v>
       </c>
       <c r="I76" s="4" t="inlineStr">
         <is>
@@ -6036,19 +6036,19 @@
         </is>
       </c>
       <c r="J76" s="6" t="n">
-        <v>45659</v>
+        <v>45962</v>
       </c>
       <c r="K76" s="6" t="n">
-        <v>46024</v>
+        <v>46023</v>
       </c>
       <c r="L76" s="4" t="n">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="5" t="inlineStr">
         <is>
-          <t>PROD-001788</t>
+          <t>PROD-001780</t>
         </is>
       </c>
       <c r="B77" s="5" t="inlineStr">
@@ -6057,30 +6057,30 @@
         </is>
       </c>
       <c r="C77" s="5" t="n">
-        <v>1788</v>
+        <v>1780</v>
       </c>
       <c r="D77" s="5" t="inlineStr">
         <is>
-          <t>19906234456</t>
+          <t>18785191088</t>
         </is>
       </c>
       <c r="E77" s="5" t="inlineStr">
         <is>
-          <t>DELT</t>
+          <t>ÉPSI</t>
         </is>
       </c>
       <c r="F77" s="5" t="inlineStr">
         <is>
-          <t>RESIDENCIAL</t>
+          <t>EQUIPAMENTOS</t>
         </is>
       </c>
       <c r="G77" s="5" t="inlineStr">
         <is>
-          <t>VIAGEM</t>
+          <t>PATRIMONIAL</t>
         </is>
       </c>
       <c r="H77" s="5" t="n">
-        <v>2654367</v>
+        <v>5166325</v>
       </c>
       <c r="I77" s="5" t="inlineStr">
         <is>
@@ -6088,19 +6088,19 @@
         </is>
       </c>
       <c r="J77" s="7" t="n">
-        <v>45663</v>
+        <v>45658</v>
       </c>
       <c r="K77" s="7" t="n">
-        <v>46028</v>
+        <v>46023</v>
       </c>
       <c r="L77" s="5" t="n">
-        <v>168</v>
+        <v>173</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="4" t="inlineStr">
         <is>
-          <t>PROD-002952</t>
+          <t>PROD-001488</t>
         </is>
       </c>
       <c r="B78" s="4" t="inlineStr">
@@ -6109,11 +6109,11 @@
         </is>
       </c>
       <c r="C78" s="4" t="n">
-        <v>2952</v>
+        <v>1488</v>
       </c>
       <c r="D78" s="4" t="inlineStr">
         <is>
-          <t>18449892665</t>
+          <t>15451680876</t>
         </is>
       </c>
       <c r="E78" s="4" t="inlineStr">
@@ -6123,16 +6123,16 @@
       </c>
       <c r="F78" s="4" t="inlineStr">
         <is>
-          <t>AUTOMÓVEL</t>
+          <t>RESIDENCIAL</t>
         </is>
       </c>
       <c r="G78" s="4" t="inlineStr">
         <is>
-          <t>PREVIDÊNCIA</t>
+          <t>VIAGEM</t>
         </is>
       </c>
       <c r="H78" s="4" t="n">
-        <v>2398549</v>
+        <v>2654367</v>
       </c>
       <c r="I78" s="4" t="inlineStr">
         <is>
@@ -6152,7 +6152,7 @@
     <row r="79">
       <c r="A79" s="5" t="inlineStr">
         <is>
-          <t>PROD-004663</t>
+          <t>PROD-002652</t>
         </is>
       </c>
       <c r="B79" s="5" t="inlineStr">
@@ -6161,30 +6161,30 @@
         </is>
       </c>
       <c r="C79" s="5" t="n">
-        <v>4663</v>
+        <v>2652</v>
       </c>
       <c r="D79" s="5" t="inlineStr">
         <is>
-          <t>14590099217</t>
+          <t>75869261796</t>
         </is>
       </c>
       <c r="E79" s="5" t="inlineStr">
         <is>
-          <t>ÉPSI</t>
+          <t>DELT</t>
         </is>
       </c>
       <c r="F79" s="5" t="inlineStr">
         <is>
-          <t>EQUIPAMENTOS</t>
+          <t>AUTOMÓVEL</t>
         </is>
       </c>
       <c r="G79" s="5" t="inlineStr">
         <is>
-          <t>PATRIMONIAL</t>
+          <t>PREVIDÊNCIA</t>
         </is>
       </c>
       <c r="H79" s="5" t="n">
-        <v>6282827</v>
+        <v>2398549</v>
       </c>
       <c r="I79" s="5" t="inlineStr">
         <is>
@@ -6192,19 +6192,19 @@
         </is>
       </c>
       <c r="J79" s="7" t="n">
-        <v>45665</v>
+        <v>45663</v>
       </c>
       <c r="K79" s="7" t="n">
-        <v>46030</v>
+        <v>46028</v>
       </c>
       <c r="L79" s="5" t="n">
-        <v>166</v>
+        <v>168</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="4" t="inlineStr">
         <is>
-          <t>PROD-001447</t>
+          <t>PROD-004363</t>
         </is>
       </c>
       <c r="B80" s="4" t="inlineStr">
@@ -6213,30 +6213,30 @@
         </is>
       </c>
       <c r="C80" s="4" t="n">
-        <v>1447</v>
+        <v>4363</v>
       </c>
       <c r="D80" s="4" t="inlineStr">
         <is>
-          <t>11266912153</t>
+          <t>64710276773</t>
         </is>
       </c>
       <c r="E80" s="4" t="inlineStr">
         <is>
-          <t>BETA</t>
+          <t>ÉPSI</t>
         </is>
       </c>
       <c r="F80" s="4" t="inlineStr">
         <is>
-          <t>EMPRESARIAL</t>
+          <t>EQUIPAMENTOS</t>
         </is>
       </c>
       <c r="G80" s="4" t="inlineStr">
         <is>
-          <t>RC</t>
+          <t>PATRIMONIAL</t>
         </is>
       </c>
       <c r="H80" s="4" t="n">
-        <v>8773056</v>
+        <v>6282827</v>
       </c>
       <c r="I80" s="4" t="inlineStr">
         <is>
@@ -6244,19 +6244,19 @@
         </is>
       </c>
       <c r="J80" s="6" t="n">
-        <v>45666</v>
+        <v>45665</v>
       </c>
       <c r="K80" s="6" t="n">
-        <v>46031</v>
+        <v>46030</v>
       </c>
       <c r="L80" s="4" t="n">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="5" t="inlineStr">
         <is>
-          <t>PROD-000782</t>
+          <t>PROD-001147</t>
         </is>
       </c>
       <c r="B81" s="5" t="inlineStr">
@@ -6265,30 +6265,30 @@
         </is>
       </c>
       <c r="C81" s="5" t="n">
-        <v>782</v>
+        <v>1147</v>
       </c>
       <c r="D81" s="5" t="inlineStr">
         <is>
-          <t>56083318195</t>
+          <t>96881435368</t>
         </is>
       </c>
       <c r="E81" s="5" t="inlineStr">
         <is>
-          <t>GAMA</t>
+          <t>BETA</t>
         </is>
       </c>
       <c r="F81" s="5" t="inlineStr">
         <is>
-          <t>AUTOMÓVEL</t>
+          <t>EMPRESARIAL</t>
         </is>
       </c>
       <c r="G81" s="5" t="inlineStr">
         <is>
-          <t>VIAGEM</t>
+          <t>RC</t>
         </is>
       </c>
       <c r="H81" s="5" t="n">
-        <v>1528602</v>
+        <v>8773056</v>
       </c>
       <c r="I81" s="5" t="inlineStr">
         <is>
@@ -6296,19 +6296,19 @@
         </is>
       </c>
       <c r="J81" s="7" t="n">
-        <v>45671</v>
+        <v>45666</v>
       </c>
       <c r="K81" s="7" t="n">
-        <v>46036</v>
+        <v>46031</v>
       </c>
       <c r="L81" s="5" t="n">
-        <v>160</v>
+        <v>165</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="4" t="inlineStr">
         <is>
-          <t>PROD-001590</t>
+          <t>PROD-000482</t>
         </is>
       </c>
       <c r="B82" s="4" t="inlineStr">
@@ -6317,11 +6317,11 @@
         </is>
       </c>
       <c r="C82" s="4" t="n">
-        <v>1590</v>
+        <v>482</v>
       </c>
       <c r="D82" s="4" t="inlineStr">
         <is>
-          <t>48728299796</t>
+          <t>13875927125</t>
         </is>
       </c>
       <c r="E82" s="4" t="inlineStr">
@@ -6336,11 +6336,11 @@
       </c>
       <c r="G82" s="4" t="inlineStr">
         <is>
-          <t>PREVIDÊNCIA</t>
+          <t>VIAGEM</t>
         </is>
       </c>
       <c r="H82" s="4" t="n">
-        <v>2432350</v>
+        <v>1528602</v>
       </c>
       <c r="I82" s="4" t="inlineStr">
         <is>
@@ -6360,7 +6360,7 @@
     <row r="83">
       <c r="A83" s="5" t="inlineStr">
         <is>
-          <t>PROD-002451</t>
+          <t>PROD-001290</t>
         </is>
       </c>
       <c r="B83" s="5" t="inlineStr">
@@ -6369,30 +6369,30 @@
         </is>
       </c>
       <c r="C83" s="5" t="n">
-        <v>2451</v>
+        <v>1290</v>
       </c>
       <c r="D83" s="5" t="inlineStr">
         <is>
-          <t>77418625652</t>
+          <t>69804204394</t>
         </is>
       </c>
       <c r="E83" s="5" t="inlineStr">
         <is>
-          <t>ETA</t>
+          <t>GAMA</t>
         </is>
       </c>
       <c r="F83" s="5" t="inlineStr">
         <is>
-          <t>RC PROFISSIONAL</t>
+          <t>AUTOMÓVEL</t>
         </is>
       </c>
       <c r="G83" s="5" t="inlineStr">
         <is>
-          <t>PATRIMONIAL</t>
+          <t>PREVIDÊNCIA</t>
         </is>
       </c>
       <c r="H83" s="5" t="n">
-        <v>1384288</v>
+        <v>2432350</v>
       </c>
       <c r="I83" s="5" t="inlineStr">
         <is>
@@ -6400,19 +6400,19 @@
         </is>
       </c>
       <c r="J83" s="7" t="n">
-        <v>45683</v>
+        <v>45671</v>
       </c>
       <c r="K83" s="7" t="n">
-        <v>46048</v>
+        <v>46036</v>
       </c>
       <c r="L83" s="5" t="n">
-        <v>148</v>
+        <v>160</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="4" t="inlineStr">
         <is>
-          <t>PROD-003858</t>
+          <t>PROD-002151</t>
         </is>
       </c>
       <c r="B84" s="4" t="inlineStr">
@@ -6421,21 +6421,21 @@
         </is>
       </c>
       <c r="C84" s="4" t="n">
-        <v>3858</v>
+        <v>2151</v>
       </c>
       <c r="D84" s="4" t="inlineStr">
         <is>
-          <t>98253092511</t>
+          <t>12499856984</t>
         </is>
       </c>
       <c r="E84" s="4" t="inlineStr">
         <is>
-          <t>BETA</t>
+          <t>ETA</t>
         </is>
       </c>
       <c r="F84" s="4" t="inlineStr">
         <is>
-          <t>VIAGEM</t>
+          <t>RC PROFISSIONAL</t>
         </is>
       </c>
       <c r="G84" s="4" t="inlineStr">
@@ -6444,7 +6444,7 @@
         </is>
       </c>
       <c r="H84" s="4" t="n">
-        <v>4037316</v>
+        <v>1384288</v>
       </c>
       <c r="I84" s="4" t="inlineStr">
         <is>
@@ -6452,19 +6452,19 @@
         </is>
       </c>
       <c r="J84" s="6" t="n">
-        <v>46022</v>
+        <v>45683</v>
       </c>
       <c r="K84" s="6" t="n">
-        <v>46053</v>
+        <v>46048</v>
       </c>
       <c r="L84" s="4" t="n">
-        <v>143</v>
+        <v>148</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="5" t="inlineStr">
         <is>
-          <t>PROD-001579</t>
+          <t>PROD-003558</t>
         </is>
       </c>
       <c r="B85" s="5" t="inlineStr">
@@ -6473,16 +6473,16 @@
         </is>
       </c>
       <c r="C85" s="5" t="n">
-        <v>1579</v>
+        <v>3558</v>
       </c>
       <c r="D85" s="5" t="inlineStr">
         <is>
-          <t>28699041379</t>
+          <t>51583281826</t>
         </is>
       </c>
       <c r="E85" s="5" t="inlineStr">
         <is>
-          <t>TETA</t>
+          <t>BETA</t>
         </is>
       </c>
       <c r="F85" s="5" t="inlineStr">
@@ -6492,11 +6492,11 @@
       </c>
       <c r="G85" s="5" t="inlineStr">
         <is>
-          <t>RC</t>
+          <t>PATRIMONIAL</t>
         </is>
       </c>
       <c r="H85" s="5" t="n">
-        <v>5119761</v>
+        <v>4037316</v>
       </c>
       <c r="I85" s="5" t="inlineStr">
         <is>
@@ -6504,19 +6504,19 @@
         </is>
       </c>
       <c r="J85" s="7" t="n">
-        <v>46001</v>
+        <v>46022</v>
       </c>
       <c r="K85" s="7" t="n">
-        <v>46063</v>
+        <v>46053</v>
       </c>
       <c r="L85" s="5" t="n">
-        <v>133</v>
+        <v>143</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="4" t="inlineStr">
         <is>
-          <t>PROD-000376</t>
+          <t>PROD-004471</t>
         </is>
       </c>
       <c r="B86" s="4" t="inlineStr">
@@ -6525,30 +6525,30 @@
         </is>
       </c>
       <c r="C86" s="4" t="n">
-        <v>376</v>
+        <v>4471</v>
       </c>
       <c r="D86" s="4" t="inlineStr">
         <is>
-          <t>33898881671</t>
+          <t>56083318195</t>
         </is>
       </c>
       <c r="E86" s="4" t="inlineStr">
         <is>
-          <t>DELT</t>
+          <t>TETA</t>
         </is>
       </c>
       <c r="F86" s="4" t="inlineStr">
         <is>
-          <t>VIAGEM</t>
+          <t>RC PROFISSIONAL</t>
         </is>
       </c>
       <c r="G86" s="4" t="inlineStr">
         <is>
-          <t>AUTO</t>
+          <t>RC</t>
         </is>
       </c>
       <c r="H86" s="4" t="n">
-        <v>8382505</v>
+        <v>9373087</v>
       </c>
       <c r="I86" s="4" t="inlineStr">
         <is>
@@ -6556,19 +6556,19 @@
         </is>
       </c>
       <c r="J86" s="6" t="n">
-        <v>45972</v>
+        <v>45688</v>
       </c>
       <c r="K86" s="6" t="n">
-        <v>46064</v>
+        <v>46053</v>
       </c>
       <c r="L86" s="4" t="n">
-        <v>132</v>
+        <v>143</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="5" t="inlineStr">
         <is>
-          <t>PROD-000428</t>
+          <t>PROD-000076</t>
         </is>
       </c>
       <c r="B87" s="5" t="inlineStr">
@@ -6577,16 +6577,16 @@
         </is>
       </c>
       <c r="C87" s="5" t="n">
-        <v>428</v>
+        <v>76</v>
       </c>
       <c r="D87" s="5" t="inlineStr">
         <is>
-          <t>64710276773</t>
+          <t>98992172233</t>
         </is>
       </c>
       <c r="E87" s="5" t="inlineStr">
         <is>
-          <t>BETA</t>
+          <t>DELT</t>
         </is>
       </c>
       <c r="F87" s="5" t="inlineStr">
@@ -6600,7 +6600,7 @@
         </is>
       </c>
       <c r="H87" s="5" t="n">
-        <v>5171554</v>
+        <v>8382505</v>
       </c>
       <c r="I87" s="5" t="inlineStr">
         <is>
@@ -6608,19 +6608,19 @@
         </is>
       </c>
       <c r="J87" s="7" t="n">
-        <v>46043</v>
+        <v>45972</v>
       </c>
       <c r="K87" s="7" t="n">
-        <v>46074</v>
+        <v>46064</v>
       </c>
       <c r="L87" s="5" t="n">
-        <v>122</v>
+        <v>132</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="4" t="inlineStr">
         <is>
-          <t>PROD-001572</t>
+          <t>PROD-004483</t>
         </is>
       </c>
       <c r="B88" s="4" t="inlineStr">
@@ -6629,30 +6629,30 @@
         </is>
       </c>
       <c r="C88" s="4" t="n">
-        <v>1572</v>
+        <v>4483</v>
       </c>
       <c r="D88" s="4" t="inlineStr">
         <is>
-          <t>98616229991</t>
+          <t>71732030937</t>
         </is>
       </c>
       <c r="E88" s="4" t="inlineStr">
         <is>
-          <t>ZETA</t>
+          <t>ALFA</t>
         </is>
       </c>
       <c r="F88" s="4" t="inlineStr">
         <is>
-          <t>RC PROFISSIONAL</t>
+          <t>EMPRESARIAL</t>
         </is>
       </c>
       <c r="G88" s="4" t="inlineStr">
         <is>
-          <t>RC</t>
+          <t>SAÚDE</t>
         </is>
       </c>
       <c r="H88" s="4" t="n">
-        <v>6269284</v>
+        <v>6775808</v>
       </c>
       <c r="I88" s="4" t="inlineStr">
         <is>
@@ -6660,19 +6660,19 @@
         </is>
       </c>
       <c r="J88" s="6" t="n">
-        <v>46105</v>
+        <v>45706</v>
       </c>
       <c r="K88" s="6" t="n">
-        <v>46075</v>
+        <v>46071</v>
       </c>
       <c r="L88" s="4" t="n">
-        <v>121</v>
+        <v>125</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="5" t="inlineStr">
         <is>
-          <t>PROD-000615</t>
+          <t>PROD-000128</t>
         </is>
       </c>
       <c r="B89" s="5" t="inlineStr">
@@ -6681,16 +6681,16 @@
         </is>
       </c>
       <c r="C89" s="5" t="n">
-        <v>615</v>
+        <v>128</v>
       </c>
       <c r="D89" s="5" t="inlineStr">
         <is>
-          <t>34163894484</t>
+          <t>13433200379</t>
         </is>
       </c>
       <c r="E89" s="5" t="inlineStr">
         <is>
-          <t>ZETA</t>
+          <t>BETA</t>
         </is>
       </c>
       <c r="F89" s="5" t="inlineStr">
@@ -6700,11 +6700,11 @@
       </c>
       <c r="G89" s="5" t="inlineStr">
         <is>
-          <t>PATRIMONIAL</t>
+          <t>AUTO</t>
         </is>
       </c>
       <c r="H89" s="5" t="n">
-        <v>5546937</v>
+        <v>5171554</v>
       </c>
       <c r="I89" s="5" t="inlineStr">
         <is>
@@ -6712,19 +6712,19 @@
         </is>
       </c>
       <c r="J89" s="7" t="n">
-        <v>46013</v>
+        <v>46043</v>
       </c>
       <c r="K89" s="7" t="n">
-        <v>46075</v>
+        <v>46074</v>
       </c>
       <c r="L89" s="5" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="4" t="inlineStr">
         <is>
-          <t>PROD-001858</t>
+          <t>PROD-000315</t>
         </is>
       </c>
       <c r="B90" s="4" t="inlineStr">
@@ -6733,30 +6733,30 @@
         </is>
       </c>
       <c r="C90" s="4" t="n">
-        <v>1858</v>
+        <v>315</v>
       </c>
       <c r="D90" s="4" t="inlineStr">
         <is>
-          <t>46287334270</t>
+          <t>25546659051</t>
         </is>
       </c>
       <c r="E90" s="4" t="inlineStr">
         <is>
-          <t>ÉPSI</t>
+          <t>ZETA</t>
         </is>
       </c>
       <c r="F90" s="4" t="inlineStr">
         <is>
-          <t>EQUIPAMENTOS</t>
+          <t>VIAGEM</t>
         </is>
       </c>
       <c r="G90" s="4" t="inlineStr">
         <is>
-          <t>AUTO</t>
+          <t>PATRIMONIAL</t>
         </is>
       </c>
       <c r="H90" s="4" t="n">
-        <v>5354050</v>
+        <v>5546937</v>
       </c>
       <c r="I90" s="4" t="inlineStr">
         <is>
@@ -6764,19 +6764,19 @@
         </is>
       </c>
       <c r="J90" s="6" t="n">
-        <v>45713</v>
+        <v>46013</v>
       </c>
       <c r="K90" s="6" t="n">
-        <v>46078</v>
+        <v>46075</v>
       </c>
       <c r="L90" s="4" t="n">
-        <v>118</v>
+        <v>121</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="5" t="inlineStr">
         <is>
-          <t>PROD-001343</t>
+          <t>PROD-001558</t>
         </is>
       </c>
       <c r="B91" s="5" t="inlineStr">
@@ -6785,11 +6785,11 @@
         </is>
       </c>
       <c r="C91" s="5" t="n">
-        <v>1343</v>
+        <v>1558</v>
       </c>
       <c r="D91" s="5" t="inlineStr">
         <is>
-          <t>69378547772</t>
+          <t>74993097289</t>
         </is>
       </c>
       <c r="E91" s="5" t="inlineStr">
@@ -6799,7 +6799,7 @@
       </c>
       <c r="F91" s="5" t="inlineStr">
         <is>
-          <t>EMPRESARIAL</t>
+          <t>EQUIPAMENTOS</t>
         </is>
       </c>
       <c r="G91" s="5" t="inlineStr">
@@ -6808,7 +6808,7 @@
         </is>
       </c>
       <c r="H91" s="5" t="n">
-        <v>7437737</v>
+        <v>5354050</v>
       </c>
       <c r="I91" s="5" t="inlineStr">
         <is>
@@ -6816,19 +6816,19 @@
         </is>
       </c>
       <c r="J91" s="7" t="n">
-        <v>45721</v>
+        <v>45713</v>
       </c>
       <c r="K91" s="7" t="n">
-        <v>46086</v>
+        <v>46078</v>
       </c>
       <c r="L91" s="5" t="n">
-        <v>110</v>
+        <v>118</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="4" t="inlineStr">
         <is>
-          <t>PROD-003217</t>
+          <t>PROD-001043</t>
         </is>
       </c>
       <c r="B92" s="4" t="inlineStr">
@@ -6837,30 +6837,30 @@
         </is>
       </c>
       <c r="C92" s="4" t="n">
-        <v>3217</v>
+        <v>1043</v>
       </c>
       <c r="D92" s="4" t="inlineStr">
         <is>
-          <t>40640909743</t>
+          <t>75304637454</t>
         </is>
       </c>
       <c r="E92" s="4" t="inlineStr">
         <is>
-          <t>ZETA</t>
+          <t>ÉPSI</t>
         </is>
       </c>
       <c r="F92" s="4" t="inlineStr">
         <is>
-          <t>RC PROFISSIONAL</t>
+          <t>EMPRESARIAL</t>
         </is>
       </c>
       <c r="G92" s="4" t="inlineStr">
         <is>
-          <t>PATRIMONIAL</t>
+          <t>AUTO</t>
         </is>
       </c>
       <c r="H92" s="4" t="n">
-        <v>6854013</v>
+        <v>7437737</v>
       </c>
       <c r="I92" s="4" t="inlineStr">
         <is>
@@ -6868,19 +6868,19 @@
         </is>
       </c>
       <c r="J92" s="6" t="n">
-        <v>45731</v>
+        <v>45721</v>
       </c>
       <c r="K92" s="6" t="n">
-        <v>46096</v>
+        <v>46086</v>
       </c>
       <c r="L92" s="4" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="5" t="inlineStr">
         <is>
-          <t>PROD-003076</t>
+          <t>PROD-002917</t>
         </is>
       </c>
       <c r="B93" s="5" t="inlineStr">
@@ -6889,16 +6889,16 @@
         </is>
       </c>
       <c r="C93" s="5" t="n">
-        <v>3076</v>
+        <v>2917</v>
       </c>
       <c r="D93" s="5" t="inlineStr">
         <is>
-          <t>83473597746</t>
+          <t>51820377889</t>
         </is>
       </c>
       <c r="E93" s="5" t="inlineStr">
         <is>
-          <t>GAMA</t>
+          <t>ZETA</t>
         </is>
       </c>
       <c r="F93" s="5" t="inlineStr">
@@ -6908,11 +6908,11 @@
       </c>
       <c r="G93" s="5" t="inlineStr">
         <is>
-          <t>RC</t>
+          <t>PATRIMONIAL</t>
         </is>
       </c>
       <c r="H93" s="5" t="n">
-        <v>3272041</v>
+        <v>6854013</v>
       </c>
       <c r="I93" s="5" t="inlineStr">
         <is>
@@ -6920,19 +6920,19 @@
         </is>
       </c>
       <c r="J93" s="7" t="n">
-        <v>45735</v>
+        <v>45731</v>
       </c>
       <c r="K93" s="7" t="n">
-        <v>46100</v>
+        <v>46096</v>
       </c>
       <c r="L93" s="5" t="n">
-        <v>96</v>
+        <v>100</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="4" t="inlineStr">
         <is>
-          <t>PROD-001852</t>
+          <t>PROD-002776</t>
         </is>
       </c>
       <c r="B94" s="4" t="inlineStr">
@@ -6941,30 +6941,30 @@
         </is>
       </c>
       <c r="C94" s="4" t="n">
-        <v>1852</v>
+        <v>2776</v>
       </c>
       <c r="D94" s="4" t="inlineStr">
         <is>
-          <t>13858542493</t>
+          <t>35031365024</t>
         </is>
       </c>
       <c r="E94" s="4" t="inlineStr">
         <is>
-          <t>ZETA</t>
+          <t>GAMA</t>
         </is>
       </c>
       <c r="F94" s="4" t="inlineStr">
         <is>
-          <t>EMPRESARIAL</t>
+          <t>RC PROFISSIONAL</t>
         </is>
       </c>
       <c r="G94" s="4" t="inlineStr">
         <is>
-          <t>VIDA</t>
+          <t>RC</t>
         </is>
       </c>
       <c r="H94" s="4" t="n">
-        <v>1729471</v>
+        <v>3272041</v>
       </c>
       <c r="I94" s="4" t="inlineStr">
         <is>
@@ -6972,19 +6972,19 @@
         </is>
       </c>
       <c r="J94" s="6" t="n">
-        <v>45737</v>
+        <v>45735</v>
       </c>
       <c r="K94" s="6" t="n">
-        <v>46102</v>
+        <v>46100</v>
       </c>
       <c r="L94" s="4" t="n">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="5" t="inlineStr">
         <is>
-          <t>PROD-001819</t>
+          <t>PROD-004456</t>
         </is>
       </c>
       <c r="B95" s="5" t="inlineStr">
@@ -6993,21 +6993,21 @@
         </is>
       </c>
       <c r="C95" s="5" t="n">
-        <v>1819</v>
+        <v>4456</v>
       </c>
       <c r="D95" s="5" t="inlineStr">
         <is>
-          <t>50375899757</t>
+          <t>86693465472</t>
         </is>
       </c>
       <c r="E95" s="5" t="inlineStr">
         <is>
-          <t>BETA</t>
+          <t>ETA</t>
         </is>
       </c>
       <c r="F95" s="5" t="inlineStr">
         <is>
-          <t>RC PROFISSIONAL</t>
+          <t>VIAGEM</t>
         </is>
       </c>
       <c r="G95" s="5" t="inlineStr">
@@ -7016,7 +7016,7 @@
         </is>
       </c>
       <c r="H95" s="5" t="n">
-        <v>9986829</v>
+        <v>7046547</v>
       </c>
       <c r="I95" s="5" t="inlineStr">
         <is>
@@ -7024,19 +7024,19 @@
         </is>
       </c>
       <c r="J95" s="7" t="n">
-        <v>45744</v>
+        <v>46042</v>
       </c>
       <c r="K95" s="7" t="n">
-        <v>46109</v>
+        <v>46101</v>
       </c>
       <c r="L95" s="5" t="n">
-        <v>87</v>
+        <v>95</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="4" t="inlineStr">
         <is>
-          <t>PROD-000253</t>
+          <t>PROD-001552</t>
         </is>
       </c>
       <c r="B96" s="4" t="inlineStr">
@@ -7045,30 +7045,30 @@
         </is>
       </c>
       <c r="C96" s="4" t="n">
-        <v>253</v>
+        <v>1552</v>
       </c>
       <c r="D96" s="4" t="inlineStr">
         <is>
-          <t>54451895202</t>
+          <t>01372151070</t>
         </is>
       </c>
       <c r="E96" s="4" t="inlineStr">
         <is>
-          <t>ALFA</t>
+          <t>ZETA</t>
         </is>
       </c>
       <c r="F96" s="4" t="inlineStr">
         <is>
-          <t>RC PROFISSIONAL</t>
+          <t>PRODUTO TESTE NAO MAPEADO</t>
         </is>
       </c>
       <c r="G96" s="4" t="inlineStr">
         <is>
-          <t>VIAGEM</t>
+          <t>VIDA</t>
         </is>
       </c>
       <c r="H96" s="4" t="n">
-        <v>1324249</v>
+        <v>1729471</v>
       </c>
       <c r="I96" s="4" t="inlineStr">
         <is>
@@ -7076,19 +7076,19 @@
         </is>
       </c>
       <c r="J96" s="6" t="n">
-        <v>45748</v>
+        <v>45737</v>
       </c>
       <c r="K96" s="6" t="n">
-        <v>46113</v>
+        <v>46102</v>
       </c>
       <c r="L96" s="4" t="n">
-        <v>83</v>
+        <v>94</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="5" t="inlineStr">
         <is>
-          <t>PROD-003542</t>
+          <t>PROD-001519</t>
         </is>
       </c>
       <c r="B97" s="5" t="inlineStr">
@@ -7097,21 +7097,21 @@
         </is>
       </c>
       <c r="C97" s="5" t="n">
-        <v>3542</v>
+        <v>1519</v>
       </c>
       <c r="D97" s="5" t="inlineStr">
         <is>
-          <t>37562890028</t>
+          <t>84902770384</t>
         </is>
       </c>
       <c r="E97" s="5" t="inlineStr">
         <is>
-          <t>ALFA</t>
+          <t>BETA</t>
         </is>
       </c>
       <c r="F97" s="5" t="inlineStr">
         <is>
-          <t>AUTOMÓVEL</t>
+          <t>RC PROFISSIONAL</t>
         </is>
       </c>
       <c r="G97" s="5" t="inlineStr">
@@ -7120,7 +7120,7 @@
         </is>
       </c>
       <c r="H97" s="5" t="n">
-        <v>5420147</v>
+        <v>9986829</v>
       </c>
       <c r="I97" s="5" t="inlineStr">
         <is>
@@ -7128,19 +7128,19 @@
         </is>
       </c>
       <c r="J97" s="7" t="n">
-        <v>45750</v>
+        <v>45744</v>
       </c>
       <c r="K97" s="7" t="n">
-        <v>46115</v>
+        <v>46109</v>
       </c>
       <c r="L97" s="5" t="n">
-        <v>81</v>
+        <v>87</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="4" t="inlineStr">
         <is>
-          <t>PROD-003443</t>
+          <t>PROD-003242</t>
         </is>
       </c>
       <c r="B98" s="4" t="inlineStr">
@@ -7149,30 +7149,30 @@
         </is>
       </c>
       <c r="C98" s="4" t="n">
-        <v>3443</v>
+        <v>3242</v>
       </c>
       <c r="D98" s="4" t="inlineStr">
         <is>
-          <t>59059929378</t>
+          <t>87653269097</t>
         </is>
       </c>
       <c r="E98" s="4" t="inlineStr">
         <is>
-          <t>BETA</t>
+          <t>ALFA</t>
         </is>
       </c>
       <c r="F98" s="4" t="inlineStr">
         <is>
-          <t>RC PROFISSIONAL</t>
+          <t>AUTOMÓVEL</t>
         </is>
       </c>
       <c r="G98" s="4" t="inlineStr">
         <is>
-          <t>AUTO</t>
+          <t>PATRIMONIAL</t>
         </is>
       </c>
       <c r="H98" s="4" t="n">
-        <v>9744546</v>
+        <v>5420147</v>
       </c>
       <c r="I98" s="4" t="inlineStr">
         <is>
@@ -7180,19 +7180,19 @@
         </is>
       </c>
       <c r="J98" s="6" t="n">
-        <v>46148</v>
+        <v>45750</v>
       </c>
       <c r="K98" s="6" t="n">
-        <v>46118</v>
+        <v>46115</v>
       </c>
       <c r="L98" s="4" t="n">
-        <v>78</v>
+        <v>81</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="5" t="inlineStr">
         <is>
-          <t>PROD-002126</t>
+          <t>PROD-001826</t>
         </is>
       </c>
       <c r="B99" s="5" t="inlineStr">
@@ -7201,11 +7201,11 @@
         </is>
       </c>
       <c r="C99" s="5" t="n">
-        <v>2126</v>
+        <v>1826</v>
       </c>
       <c r="D99" s="5" t="inlineStr">
         <is>
-          <t>13433200379</t>
+          <t>59255562588</t>
         </is>
       </c>
       <c r="E99" s="5" t="inlineStr">
@@ -7244,7 +7244,7 @@
     <row r="100">
       <c r="A100" s="4" t="inlineStr">
         <is>
-          <t>PROD-001860</t>
+          <t>PROD-001560</t>
         </is>
       </c>
       <c r="B100" s="4" t="inlineStr">
@@ -7253,11 +7253,11 @@
         </is>
       </c>
       <c r="C100" s="4" t="n">
-        <v>1860</v>
+        <v>1560</v>
       </c>
       <c r="D100" s="4" t="inlineStr">
         <is>
-          <t>46287334270</t>
+          <t>74993097289</t>
         </is>
       </c>
       <c r="E100" s="4" t="inlineStr">
@@ -7296,7 +7296,7 @@
     <row r="101">
       <c r="A101" s="5" t="inlineStr">
         <is>
-          <t>PROD-002206</t>
+          <t>PROD-001906</t>
         </is>
       </c>
       <c r="B101" s="5" t="inlineStr">
@@ -7305,11 +7305,11 @@
         </is>
       </c>
       <c r="C101" s="5" t="n">
-        <v>2206</v>
+        <v>1906</v>
       </c>
       <c r="D101" s="5" t="inlineStr">
         <is>
-          <t>47284639208</t>
+          <t>42843479552</t>
         </is>
       </c>
       <c r="E101" s="5" t="inlineStr">
@@ -7348,7 +7348,7 @@
     <row r="102">
       <c r="A102" s="4" t="inlineStr">
         <is>
-          <t>PROD-003935</t>
+          <t>PROD-002459</t>
         </is>
       </c>
       <c r="B102" s="4" t="inlineStr">
@@ -7357,11 +7357,11 @@
         </is>
       </c>
       <c r="C102" s="4" t="n">
-        <v>3935</v>
+        <v>2459</v>
       </c>
       <c r="D102" s="4" t="inlineStr">
         <is>
-          <t>46688937346</t>
+          <t>17187026217</t>
         </is>
       </c>
       <c r="E102" s="4" t="inlineStr">
@@ -7371,16 +7371,16 @@
       </c>
       <c r="F102" s="4" t="inlineStr">
         <is>
-          <t>RC PROFISSIONAL</t>
+          <t>EQUIPAMENTOS</t>
         </is>
       </c>
       <c r="G102" s="4" t="inlineStr">
         <is>
-          <t>SAÚDE</t>
+          <t>AUTO</t>
         </is>
       </c>
       <c r="H102" s="4" t="n">
-        <v>5741570</v>
+        <v>34894832025</v>
       </c>
       <c r="I102" s="4" t="inlineStr">
         <is>
@@ -7400,7 +7400,7 @@
     <row r="103">
       <c r="A103" s="5" t="inlineStr">
         <is>
-          <t>PROD-002759</t>
+          <t>PROD-003635</t>
         </is>
       </c>
       <c r="B103" s="5" t="inlineStr">
@@ -7409,11 +7409,11 @@
         </is>
       </c>
       <c r="C103" s="5" t="n">
-        <v>2759</v>
+        <v>3635</v>
       </c>
       <c r="D103" s="5" t="inlineStr">
         <is>
-          <t>02786814473</t>
+          <t>42701039308</t>
         </is>
       </c>
       <c r="E103" s="5" t="inlineStr">
@@ -7423,16 +7423,16 @@
       </c>
       <c r="F103" s="5" t="inlineStr">
         <is>
-          <t>EQUIPAMENTOS</t>
+          <t>RC PROFISSIONAL</t>
         </is>
       </c>
       <c r="G103" s="5" t="inlineStr">
         <is>
-          <t>AUTO</t>
+          <t>SAÚDE</t>
         </is>
       </c>
       <c r="H103" s="5" t="n">
-        <v>34894832025</v>
+        <v>5741570</v>
       </c>
       <c r="I103" s="5" t="inlineStr">
         <is>
@@ -7452,7 +7452,7 @@
     <row r="104">
       <c r="A104" s="4" t="inlineStr">
         <is>
-          <t>PROD-002110</t>
+          <t>PROD-001810</t>
         </is>
       </c>
       <c r="B104" s="4" t="inlineStr">
@@ -7461,11 +7461,11 @@
         </is>
       </c>
       <c r="C104" s="4" t="n">
-        <v>2110</v>
+        <v>1810</v>
       </c>
       <c r="D104" s="4" t="inlineStr">
         <is>
-          <t>17187026217</t>
+          <t>76973577907</t>
         </is>
       </c>
       <c r="E104" s="4" t="inlineStr">
@@ -7504,7 +7504,7 @@
     <row r="105">
       <c r="A105" s="5" t="inlineStr">
         <is>
-          <t>PROD-000630</t>
+          <t>PROD-000330</t>
         </is>
       </c>
       <c r="B105" s="5" t="inlineStr">
@@ -7513,11 +7513,11 @@
         </is>
       </c>
       <c r="C105" s="5" t="n">
-        <v>630</v>
+        <v>330</v>
       </c>
       <c r="D105" s="5" t="inlineStr">
         <is>
-          <t>13836702410</t>
+          <t>56342160733</t>
         </is>
       </c>
       <c r="E105" s="5" t="inlineStr">
@@ -7556,7 +7556,7 @@
     <row r="106">
       <c r="A106" s="4" t="inlineStr">
         <is>
-          <t>PROD-001236</t>
+          <t>PROD-000936</t>
         </is>
       </c>
       <c r="B106" s="4" t="inlineStr">
@@ -7565,11 +7565,11 @@
         </is>
       </c>
       <c r="C106" s="4" t="n">
-        <v>1236</v>
+        <v>936</v>
       </c>
       <c r="D106" s="4" t="inlineStr">
         <is>
-          <t>80841241182</t>
+          <t>24508821009</t>
         </is>
       </c>
       <c r="E106" s="4" t="inlineStr">
@@ -7608,7 +7608,7 @@
     <row r="107">
       <c r="A107" s="5" t="inlineStr">
         <is>
-          <t>PROD-001673</t>
+          <t>PROD-001373</t>
         </is>
       </c>
       <c r="B107" s="5" t="inlineStr">
@@ -7617,11 +7617,11 @@
         </is>
       </c>
       <c r="C107" s="5" t="n">
-        <v>1673</v>
+        <v>1373</v>
       </c>
       <c r="D107" s="5" t="inlineStr">
         <is>
-          <t>41395376724</t>
+          <t>61847870050</t>
         </is>
       </c>
       <c r="E107" s="5" t="inlineStr">
@@ -7660,7 +7660,7 @@
     <row r="108">
       <c r="A108" s="4" t="inlineStr">
         <is>
-          <t>PROD-002260</t>
+          <t>PROD-001960</t>
         </is>
       </c>
       <c r="B108" s="4" t="inlineStr">
@@ -7669,11 +7669,11 @@
         </is>
       </c>
       <c r="C108" s="4" t="n">
-        <v>2260</v>
+        <v>1960</v>
       </c>
       <c r="D108" s="4" t="inlineStr">
         <is>
-          <t>90604805892</t>
+          <t>91630097925</t>
         </is>
       </c>
       <c r="E108" s="4" t="inlineStr">
@@ -7712,7 +7712,7 @@
     <row r="109">
       <c r="A109" s="5" t="inlineStr">
         <is>
-          <t>PROD-002378</t>
+          <t>PROD-002078</t>
         </is>
       </c>
       <c r="B109" s="5" t="inlineStr">
@@ -7721,11 +7721,11 @@
         </is>
       </c>
       <c r="C109" s="5" t="n">
-        <v>2378</v>
+        <v>2078</v>
       </c>
       <c r="D109" s="5" t="inlineStr">
         <is>
-          <t>80940244550</t>
+          <t>18835523124</t>
         </is>
       </c>
       <c r="E109" s="5" t="inlineStr">
@@ -7764,7 +7764,7 @@
     <row r="110">
       <c r="A110" s="4" t="inlineStr">
         <is>
-          <t>PROD-003692</t>
+          <t>PROD-003392</t>
         </is>
       </c>
       <c r="B110" s="4" t="inlineStr">
@@ -7773,11 +7773,11 @@
         </is>
       </c>
       <c r="C110" s="4" t="n">
-        <v>3692</v>
+        <v>3392</v>
       </c>
       <c r="D110" s="4" t="inlineStr">
         <is>
-          <t>81273585730</t>
+          <t>55449647598</t>
         </is>
       </c>
       <c r="E110" s="4" t="inlineStr">
@@ -7825,10 +7825,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="17" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="11" customWidth="1" min="4" max="4"/>
@@ -7889,36 +7889,160 @@
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>Corretor Exemplo</t>
+          <t>Carla Seguros</t>
         </is>
       </c>
       <c r="B2" s="4" t="n">
-        <v>193</v>
+        <v>45</v>
       </c>
       <c r="C2" s="4" t="n">
-        <v>188</v>
+        <v>43</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>188</v>
+        <v>43</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>188</v>
+        <v>43</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>92</v>
+        <v>23</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>97.40000000000001</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="H2" s="4" t="n">
-        <v>97.40000000000001</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="I2" s="4" t="n">
-        <v>97.40000000000001</v>
+        <v>95.59999999999999</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>Diego Comercial</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="n">
+        <v>42</v>
+      </c>
+      <c r="C3" s="5" t="n">
+        <v>42</v>
+      </c>
+      <c r="D3" s="5" t="n">
+        <v>42</v>
+      </c>
+      <c r="E3" s="5" t="n">
+        <v>42</v>
+      </c>
+      <c r="F3" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="G3" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="H3" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="I3" s="5" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>Ana Vendas</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="n">
+        <v>41</v>
+      </c>
+      <c r="C4" s="4" t="n">
+        <v>39</v>
+      </c>
+      <c r="D4" s="4" t="n">
+        <v>39</v>
+      </c>
+      <c r="E4" s="4" t="n">
+        <v>39</v>
+      </c>
+      <c r="F4" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="G4" s="4" t="n">
+        <v>95.09999999999999</v>
+      </c>
+      <c r="H4" s="4" t="n">
+        <v>95.09999999999999</v>
+      </c>
+      <c r="I4" s="4" t="n">
+        <v>95.09999999999999</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>Bruno Corretor</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>33</v>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>33</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>33</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>33</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>22</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="I5" s="5" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Equipe Digital</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="C6" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="D6" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="E6" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="F6" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="G6" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="H6" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="I6" s="4" t="n">
+        <v>100</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I2"/>
+  <autoFilter ref="A1:I6"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -7929,10 +8053,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="17" customWidth="1" min="1" max="1"/>
+    <col width="27" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="17" customWidth="1" min="3" max="3"/>
     <col width="23" customWidth="1" min="4" max="4"/>
@@ -7963,65 +8087,65 @@
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>EMPRESARIAL</t>
+          <t>EQUIPAMENTOS</t>
         </is>
       </c>
       <c r="B2" s="4" t="n">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="C2" s="4" t="n">
         <v>3</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>6.976744186046512</v>
+        <v>8.333333333333332</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>RESIDENCIAL</t>
+          <t>EMPRESARIAL</t>
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="C3" s="5" t="n">
         <v>3</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>5.88235294117647</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>EQUIPAMENTOS</t>
+          <t>RC PROFISSIONAL</t>
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="C4" s="4" t="n">
         <v>2</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>5.128205128205128</v>
+        <v>4.347826086956522</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>RC PROFISSIONAL</t>
+          <t>RESIDENCIAL</t>
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="C5" s="5" t="n">
         <v>2</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>4.347826086956522</v>
+        <v>4.081632653061225</v>
       </c>
     </row>
     <row r="6">
@@ -8031,23 +8155,23 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C6" s="4" t="n">
         <v>3</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>2.941176470588235</v>
+        <v>3.03030303030303</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>VIAGEM</t>
+          <t>PRODUTO TESTE NAO MAPEADO</t>
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>32</v>
+        <v>1</v>
       </c>
       <c r="C7" s="5" t="n">
         <v>0</v>
@@ -8056,8 +8180,24 @@
         <v>0</v>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>VIAGEM</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="n">
+        <v>35</v>
+      </c>
+      <c r="C8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D7"/>
+  <autoFilter ref="A1:D8"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -8149,10 +8289,10 @@
         <v>46543</v>
       </c>
       <c r="C2" s="4" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>4780</v>
+        <v>4838</v>
       </c>
       <c r="E2" s="4" t="n">
         <v>432</v>
@@ -8174,7 +8314,7 @@
       </c>
       <c r="K2" s="4" t="inlineStr">
         <is>
-          <t>Produção janelada em 2024-03-27..2027-06-05 (38 meses): cohort/safra, snapshot mensal e somas (curva ABC, prêmio histórico do winback) refletem só esta janela — não são valores vitalícios. A 1ª safra (2024-03) tende a estar inflada por contratos iniciados antes do corte.</t>
+          <t>Produção janelada em 2024-03-27..2027-06-05 (37 meses): cohort/safra, snapshot mensal e somas (curva ABC, prêmio histórico do winback) refletem só esta janela — não são valores vitalícios. A 1ª safra (2024-03) tende a estar inflada por contratos iniciados antes do corte.</t>
         </is>
       </c>
     </row>
